--- a/results/ad-oxygen-literature-20261006/oxygen_response_review/spatial_gas_transfer/spatial_gas_transfer_cumulative.xlsx
+++ b/results/ad-oxygen-literature-20261006/oxygen_response_review/spatial_gas_transfer/spatial_gas_transfer_cumulative.xlsx
@@ -20,17 +20,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未处理续跑" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文献与专题筛选'!$A$1:$AC$234</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'三维结构与定位'!$A$1:$K$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'传质参数及剖面'!$A$1:$P$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'细胞间与絮体间'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'供氧控制'!$A$1:$Q$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'文献与专题筛选'!$A$1:$AL$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'三维结构与定位'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'传质参数及剖面'!$A$1:$P$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'细胞间与絮体间'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'供氧控制'!$A$1:$Q$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'已执行本地检索'!$A$1:$L$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'在线待执行检索'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'引用追溯'!$A$1:$K$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'种子核对'!$A$1:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'待全文与疑点'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'未处理续跑'!$A$1:$E$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'待全文与疑点'!$A$1:$H$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'未处理续跑'!$A$1:$E$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC234"/>
+  <dimension ref="A1:AL234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,51 @@
           <t>old_scope_judgment_changed</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>author_metadata_source</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>substrate</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>aggregate_or_biofilm_size</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>reactor_structure</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>context_not_reported_or_unchecked</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -855,7 +900,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Guiot, S R", "Kuhn, R", "Lévesque, M J", "Cimpoia, R"]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -929,6 +974,16 @@
       <c r="AC5" t="b">
         <v>0</v>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/cfc7af329ca2b6a6948e25003e2b6ddc6f91b2e2dc3e867e63108f407191f658.body</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -973,7 +1028,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Satoh, Hisashi", "Miura, Yuki", "Tsushima, Ikuo", "Okabe, Satoshi"]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1047,6 +1102,31 @@
       <c r="AC6" t="b">
         <v>0</v>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/cfc7af329ca2b6a6948e25003e2b6ddc6f91b2e2dc3e867e63108f407191f658.body</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>产甲烷厌氧颗粒</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>FISH与CH4/H2/pH/ORP微传感器；Deff测量方法待正文</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>已保存官方完整摘要；PMID17905889</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1168,7 +1248,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Wrede, Christoph", "Heller, Christina", "Reitner, Joachim", "Hoppert, Michael"]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1178,17 +1258,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>同一切片的光/电子显微相关成像，可区分EPS与细胞</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1199,6 +1284,52 @@
       <c r="Q8" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>C 天然成像方法</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>黑海冷泉微生物席用树脂切片和荧光/胶体金凝集素定位EPS，比较光学与电镜图</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是切片相关显微，并非已核实整颗粒三维重建；EPS黏附/矿化作用不等于氧屏障或孔隙流量</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>["成像方法"]</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>{"method": "树脂切片，光/电镜相关成像＋凝集素标记EPS", "targets": ["EPS", "细菌/古菌聚集"], "true_3D_verified": false, "EPS_pore_flow_measured": false}</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/cfc7af329ca2b6a6948e25003e2b6ddc6f91b2e2dc3e867e63108f407191f658.body</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -1314,6 +1445,11 @@
       <c r="AC9" t="b">
         <v>0</v>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2667,7 +2803,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Hamilton, Joshua J", "Calixto Contreras, Montserrat", "Reed, Jennifer L"]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2741,6 +2877,16 @@
       <c r="AC27" t="b">
         <v>0</v>
       </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/1986329a541e64ec6ec832c62ee17bee05ca3f6c784fb52bd53d2341f1a1f8d9.body</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2795,17 +2941,22 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>生物膜厚度、CH4供给及DO共存窗口的模型对照</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2816,6 +2967,42 @@
       <c r="Q28" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>C DAMO/Anammox模型</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>模型在特定氮负荷和底物比下计算出约0.17 g/m³主体DO时脱氮最佳</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>这是模型条件下结果，不是实测通用DO最佳值；模型参数来源、校准范围待全文</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>["扩散—反应模型（非产甲烷）"]</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3738,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Gambelli, Lavinia", "Guerrero-Cruz, Simon", "Mesman, Rob J", "Cremers, Geert", "Jetten, Mike S M", "Op den Camp, Huub J M", "Kartal, Boran", "Lueke, Claudia", "van Niftrik, Laura"]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3561,17 +3748,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>摘要明确采用电子断层成像，提供真正3D方法线索但不是完整AD颗粒CT</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3582,6 +3774,72 @@
       <c r="Q38" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>C 厌氧甲烷氧化富集</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>FISH/免疫金/电子断层揭示Ca.Methanoperedens细胞约1.5 μm、管状突出和候选细胞接触结构</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>电子断层方法由摘要明确；本轮未读正文确认重建体积/分辨率；细胞接触功能未证，不能认定导电或气体通道</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>["细胞尺度三维结构线索"]</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>{"method": "含electron tomography的光/电镜、FISH、免疫金", "three_D_method_reported_in_abstract": true, "fulltext_3D_verified": false, "whole_aggregate_3D_verified": false, "targets": ["古菌细胞/候选接触结构"], "EPS_pore_flow_measured": false}</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/e166bfe4cd7869ec8a1ec5334e976cbb79eb0000a28977d529a4b257b2903f1c.body</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>硝酸盐依赖厌氧甲烷氧化富集</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>古菌细胞约1.5 μm；不是整聚集体直径</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>electron tomography、光/电镜、FISH和免疫金（摘要）</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>保存的官方完整摘要；正文体重建范围待核</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -3774,6 +4032,11 @@
       <c r="AC40" t="b">
         <v>0</v>
       </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4434,7 +4697,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Trego, Anna Christine", "O'Sullivan, Sarah", "Quince, Christopher", "Mills, Simon", "Ijaz, Umer Zeeshan", "Collins, Gavin"]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4508,6 +4771,16 @@
       <c r="AC49" t="b">
         <v>0</v>
       </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/36328184af1a8747e4473dc767f2753f5f61f250c369017f68b452c5d63ba90a.body</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5014,7 +5287,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Doloman, Anna", "Boeren, Sjef", "Miller, Charles D", "Sousa, Diana Z"]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5024,17 +5297,22 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>加入第三菌后功能与聚集观察，但不把聚集当传质证明</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5045,6 +5323,57 @@
       <c r="Q56" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>A 互营共培养</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Trichococcus加入Syntrophomonas—产甲烷菌共培养后丁酸消费和甲烷率升高；SEM见共聚集倾向</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>功能提高可能涉及信号调节或酶表达，不证明距离缩短导致H2/甲酸通量提高；非真三维成像</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>["细胞间交换（间接）"]</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>{"method": "SEM表面形态，未核实三维重建", "true_3D_verified": false}</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>{"carrier": ["H2/formate（互营背景，具体分摊未实测）"], "evidence": "加入伙伴干预＋速率和SEM，交换路径仍待证", "interfloc_exchange_measured": false, "cell_distance_measured": false}</t>
+        </is>
+      </c>
+      <c r="AB56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/4c7b9de88dc3c2b30f7806e60e8ba11074b3948ba15c7089ac42c3b2eb226dd9.body</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -5178,17 +5507,22 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>基因组模型预测H2/CO2及甲酸交换，不直接等于扩散参数</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5199,6 +5533,47 @@
       <c r="Q58" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>A CO2甲烷化生物膜</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>4个外置沼气升级反应器扩散装置上的生物膜，基因组/通量平衡预测甲酸和氨基酸交换网络</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>共同出现和FBA不是物质通量/细胞间距离实测；不把名称flux balance当已经测到通量</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>["细胞间交换（模型）"]</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>{"carrier": ["H2", "CO2", "formate", "amino acids"], "evidence": "基因组重建＋通量平衡模型", "interfloc_exchange_measured": false, "cell_distance_measured": false}</t>
+        </is>
+      </c>
+      <c r="AB58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5697,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Day, Leslie A", "Kelsey, Elisa L", "Fonseca, Dallas R", "Costa, Kyle C"]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5396,6 +5771,16 @@
       <c r="AC60" t="b">
         <v>0</v>
       </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/4c7b9de88dc3c2b30f7806e60e8ba11074b3948ba15c7089ac42c3b2eb226dd9.body</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5758,17 +6143,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>层状载体提高生物量保留/反应率，涉及结构与功能</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5779,6 +6169,42 @@
       <c r="Q65" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>C 甲烷氧化脱氮膜</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>多孔聚氨酯层状膜提高硝酸盐去除、甲烷氧化和生物量保留，作者解释形成缺氧区/交叉营养</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>不是产甲烷AD；多个性质共变，面积反应通量不是kLa或Deff，局部DO未核实</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>["膜生物膜反应", "载体结构"]</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -6066,17 +6492,22 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>半固体琼脂中的CH4—O2反向梯度方法</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6087,6 +6518,42 @@
       <c r="Q69" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>C 甲烷氧化方法</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>梯度注射器重建CH4/O2反向梯度，提供均一悬浮培养看不到的空间表型</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>方法参考，非AD原始颗粒；介质扩散条件不同，不能用琼脂代替污泥Deff</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>["反向扩散梯度方法"]</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -6672,7 +7139,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Li, Dong", "Huang, Tao", "Wu, Boran", "Wang, Chengxian", "Jiang, Xiupeng", "Huang, Sheng", "Dai, Xiaohu", "Chai, Xiaoli"]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6682,17 +7149,22 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>附着/悬浮分级与菌群生态位，反对套用古菌总在中心的统一图式</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -6703,6 +7175,52 @@
       <c r="Q77" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>A 产甲烷AD载体</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>10 g/L硅藻土使甲烷提高11.76%；发酵菌偏紧密附着，产乙酸型与氢营养古菌富集于悬浮组</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>群落分级不是三维细胞坐标，电子传递/互营解释未测H2/甲酸通量；载体吸附与缓冲亦可能参与</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>["附着/悬浮分工"]</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>{"method": "群落分级/生物膜和EPS；三维位置未核实", "true_3D_verified": false}</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/863e1adc64fc7079316bfb5f12b86c02fb0085e72978511e95d4520981794eb8.body</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -7760,17 +8278,22 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>用于区分电子传递与气体物质传质，不据导电材料推气体通道</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -7781,6 +8304,42 @@
       <c r="Q91" t="inlineStr">
         <is>
           <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>B 界面电子传递背景</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>膜固定nZVI使生物量贴近并改善去除/甲烷；EET标记随铁状态变化，含非生物/基质贡献</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>未提供本轮已核实H2/甲酸物质通量/距离；电子传递研究不能自动算物质传质证据</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>["界面电子传递（非气体传质证明）"]</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -8296,6 +8855,41 @@
       <c r="AC97" t="b">
         <v>0</v>
       </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>人工产甲烷—甲烷氧化共培养MBR</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>乙酸26.2 mM；CH4/CO2等混合气供给</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>室温约20°C</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>1.5 L工作体积，150 rpm；沉降/排出选择聚集体</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>FISH、主体DO与进出气体浓度；非已核实3D</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Materials and methods/Reactor set-up; Co-cultivation; FISH microscopy；Results/Start-up</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8842,17 +9436,22 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>氧冲击下生物膜分层的作者解释与可见抑制</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8868,6 +9467,47 @@
       <c r="R104" t="inlineStr">
         <is>
           <t>符合本轮核心范围</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>C DAMO/Anammox</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>DO0.2 mg/L时目标类群显著下降，0.5 mg/L出现硝酸盐积累；作者提出外层替代保护内层</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>仅摘要未确认氧微剖面或因果保护；不是产甲烷AD；功能基因下降非速率</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>["局部暴露（解释）"]</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>{"method": "分层保护来自作者解释；三维/局部DO测量待正文", "true_3D_verified": false}</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -9002,17 +9642,22 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>有机物影响氧穿透及铁循环，揭示反应—扩散耦合</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -9028,6 +9673,42 @@
       <c r="R106" t="inlineStr">
         <is>
           <t>核心候选</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>C Anammox方法参照</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>摘要称30–110 mg COD/L改变微氧颗粒DO穿透，促进分层铁氧化还原和脱氮</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>无本轮已核实穿透深度值或微探针/模型具体方法；不是产甲烷AD，基因暗示不能当通量</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>["聚集体内氧穿透（方法待核）"]</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -10479,17 +11160,22 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>海绵生物膜位置、活性和生存测量区分</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10505,6 +11191,47 @@
       <c r="R124" t="inlineStr">
         <is>
           <t>核心候选</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>C 脱氮生物膜方法</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>FISH与离子微电极显示侧面/中心菌群不同，生物量随深度减而存活率不表现同样空间变化，Anammox贯穿深度</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>空间位置不等于相同DO，非产甲烷菌；摘要FISH不自动算3D体重建</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>["生物膜类群/功能剖面"]</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>{"method": "FISH与NH4/NO3微电极；三维未核实", "true_3D_verified": false}</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL124" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -11280,6 +12007,31 @@
       </c>
       <c r="AC133" t="b">
         <v>0</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>天然沿岸沉积物完整柱芯</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>保留界面结构，上覆水曝气，分时取样</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>氧微剖面＋群落/转录</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Results/Chemical fluxes；原evidence_sources JSON</t>
+        </is>
+      </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -12856,6 +13608,31 @@
       <c r="AC152" t="b">
         <v>0</v>
       </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Anammox颗粒，非产甲烷AD</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>平均直径约5 mm（摘要）</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>NH4/NO2/NO3/pH微电极；非O2微剖面</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>完整缓存摘要</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12979,6 +13756,31 @@
       <c r="AC153" t="b">
         <v>0</v>
       </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>厌氧下水道生物膜</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>平均厚约800 μm（摘要）</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>切片FISH、微电极、模型（摘要）</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>完整缓存摘要</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13339,6 +14141,11 @@
       <c r="AC157" t="b">
         <v>0</v>
       </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13803,17 +14610,22 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>生物膜厚度及局部ORP/硫化物，但不是O2实测</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -13829,6 +14641,47 @@
       <c r="R163" t="inlineStr">
         <is>
           <t>待全文确认</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>C 下水道生物膜</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>45 d厚约1.2 mm，局部ORP−105 mV及约0.1 μmol/L硫化物；结构和类群变化相关</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>负ORP不是直接DO证明；微电极种类要分清，不把ORP剖面写为氧剖面</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>["局部ORP/硫化物"]</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>{"method": "微结构分析＋微电极；三维方法未核实", "true_3D_verified": false}</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -15842,6 +16695,11 @@
       <c r="AC187" t="b">
         <v>0</v>
       </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -16416,6 +17274,11 @@
       <c r="AC194" t="b">
         <v>0</v>
       </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16539,6 +17402,41 @@
       <c r="AC195" t="b">
         <v>0</v>
       </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>平行AD反应器</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>初级污泥，曾以MgSO4提高硫负荷</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>35.0±0.2°C</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>液体50 L，顶空约20 L；底部陶瓷扩散器</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>ORP反馈、日气体组成、SCADA；未核实DO</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>PDF p2 §2.1–2.2，p3 §2.3–2.4</t>
+        </is>
+      </c>
+      <c r="AL195" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -16822,6 +17720,41 @@
       <c r="AC198" t="b">
         <v>0</v>
       </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>奶牛粪AD及消化液脱硫单元</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>奶牛粪/消化液及沼气H2S</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>脱硫桶20–25°C；不等同田间全部运行条件</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>65/104 L桶；液面0.099/0.150 m²等；另竖直润湿布</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>面积干预、气相O2/H2S/CH4测量、气流与去除率</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>PDF p3–4 Methods，p7–8结果与Table1</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -17204,17 +18137,22 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>纳米气泡水对纤维素AD影响，谨防把水的弛豫测量当气体D</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -17230,6 +18168,42 @@
       <c r="R203" t="inlineStr">
         <is>
           <t>核心候选</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>A AD气泡处理</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>空气/CO2纳米气泡水提高后期甲烷与纤维素利用；报告水分子质子弛豫时间2611–2906 ms</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>弛豫时间不是H2/CH4/O2扩散系数或气泡穿过污泥的直接证据；化学/底物效应需分开</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>["气液界面（解释）"]</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -17515,6 +18489,11 @@
       <c r="AC206" t="b">
         <v>0</v>
       </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -17569,17 +18548,22 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>用空气混合与沼气/机械/不混合比较，涉及混合与氧共变</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -17595,6 +18579,42 @@
       <c r="R207" t="inlineStr">
         <is>
           <t>核心候选</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>A AD混合干预</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>相同功率下摘要报告均匀混合时间由10 min缩短到1.5 min，甲烷及水解改善</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>氧输入和对流同时改变；62.9%/37.1%的贡献分摊方法需正文核；混合时间不是Deff、kf或kLa</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>["主体混合", "气液供氧"]</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>[{"symbol": "bulk homogeneous mixing time", "value_original": "10 versus 1.5", "unit_original": "min", "acquisition": "摘要报告同功率混合试验；示踪/拟合细节待全文", "condition": "机械混合vs空气混合；动物废水AD", "source_locator": "完整缓存摘要", "not_equal_to": "不是聚集体内部Deff或细胞间距离"}]</t>
+        </is>
+      </c>
+      <c r="AB207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -17719,6 +18739,36 @@
       </c>
       <c r="AC208" t="b">
         <v>0</v>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>产甲烷2 L CSTR</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>象草；OLR1.5升至5.0 g VS/L/d</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>间歇ORP相对基线微曝气；非颗粒空间分布测量</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>宏基因组重建＋ORP控制，未给本轮已核实局部DO</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>PDF p2 §2.1</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -17990,6 +19040,11 @@
       <c r="AC211" t="b">
         <v>0</v>
       </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -18118,17 +19173,22 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>微气泡界面与生物过程综述，非统一传质常数来源</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -18144,6 +19204,42 @@
       <c r="R213" t="inlineStr">
         <is>
           <t>机制背景</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>导航综述</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>提出小气泡表面积、界面聚集和产品移除可能促进传递</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>综述中气相/液相扩散差异不能直接移植为活性颗粒的气体Deff；需回到原始试验</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>["气液界面（综述）"]</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -18676,17 +19772,22 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>设计/控制/监测综述可追溯原始ORP、H2S反馈研究</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -18702,6 +19803,42 @@
       <c r="R220" t="inlineStr">
         <is>
           <t>机制背景</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>导航综述</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>比较液相/气相注入、空气/纯氧、剂量及PID控制，指出水解和甲烷效应不一致</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>不能从综述给出通用ORP—DO换算、推荐设定值或控制收益；优先原始方法</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>["控制综述"]</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL220" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -18996,6 +20133,11 @@
       <c r="AC223" t="b">
         <v>0</v>
       </c>
+      <c r="AL223" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -19050,17 +20192,22 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>LCFA连续反应器的空间与恢复相关背景</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -19076,6 +20223,42 @@
       <c r="R224" t="inlineStr">
         <is>
           <t>核心候选</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>A 产甲烷直接</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>ORP约−350/−250 mV的反应器中，高负荷微氧组积累更多棕榈酸且恢复产甲烷活性；兼性菌与LCFA组成相关</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>本轮依据摘要，不把ORP当DO反馈实测；生物膜相关不等于量得H2通量或特定互作</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>["群落/生物膜关联"]</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -19538,17 +20721,22 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>纳米气泡AD综述的机制与方法线索</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -19564,6 +20752,42 @@
       <c r="R230" t="inlineStr">
         <is>
           <t>机制背景</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>导航综述</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>汇总底物流动/酶活性和产气改善可能机制</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>不是独立传质实测；气泡水、溶解气体和颗粒内扩散不能混用</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>["气液界面（综述）"]</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL230" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -19604,17 +20828,22 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>摘要初筛</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>尚未专题判断</t>
+          <t>专题相关</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>本轮未阅读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>ORP相对基线控制的原库线索，不能与后续R07202当独立重复</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -19630,6 +20859,47 @@
       <c r="R231" t="inlineStr">
         <is>
           <t>核心候选</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>待核实研究线索</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>摘要称每24 h引入ORP基线+25 mV控制后VFA下降56%、甲烷提高252%</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>年/期刊/DOI尚缺；与R07202研究链的暴露频率表述不同，需核身份和前文，不当独立支持</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>["主体ORP控制"]</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>{"type": "摘要报告ORP间歇反馈，元数据待核", "setpoint": "+25 mV above baseline", "logic": "摘要称every24h，与R07202每隔一天不可混写", "oxygen_input": "未核", "DO": "未核", "oxygen_consumption": "未核", "spatial_oxygen_profile": "未核", "reference_electrode": "未核", "locator": "原库完整摘要"}</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL231" t="inlineStr">
+        <is>
+          <t>空值表示本轮尚未核实，不能推断原文未报告</t>
         </is>
       </c>
     </row>
@@ -19860,7 +21130,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC234"/>
+  <autoFilter ref="A1:AL234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19871,7 +21141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19993,17 +21263,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ODS-PMID19490126</t>
+          <t>ODS-PMID18405985</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.1111/j.1574-6941.2009.00680.x</t>
+          <t>10.1016/j.mimet.2008.02.020</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecophysiology of syntrophic communities that degrade saturated and unsaturated long-chain fatty acids.</t>
+          <t>Correlative light/electron microscopy for the investigation of microbial mats from Black Sea Cold Seeps.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20013,7 +21283,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>不是独立原始测定；不能从综述抽一个统一Deff或把细胞受抑唯一归于扩散</t>
+          <t>是切片相关显微，并非已核实整颗粒三维重建；EPS黏附/矿化作用不等于氧屏障或孔隙流量</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -20030,17 +21300,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ODS-PMID26147299</t>
+          <t>ODS-PMID19490126</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.1371/journal.pcbi.1004364</t>
+          <t>10.1111/j.1574-6941.2009.00680.x</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thermodynamics and H2 Transfer in a Methanogenic, Syntrophic Community.</t>
+          <t>Ecophysiology of syntrophic communities that degrade saturated and unsaturated long-chain fatty acids.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20050,7 +21320,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>代谢网络/热力学模型，不是实测细胞间距离、Deff或絮体间kf；不能将预测交换当已测物质通量</t>
+          <t>不是独立原始测定；不能从综述抽一个统一Deff或把细胞受抑唯一归于扩散</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -20067,17 +21337,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ODS-PMID30236845</t>
+          <t>ODS-PMID26147299</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.1016/j.scitotenv.2018.09.184</t>
+          <t>10.1371/journal.pcbi.1004364</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mass transfer affects reactor performance, microbial morphology, and community succession in the methane-dependent denitrification and anaerobic ammonium oxidation co-culture.</t>
+          <t>Thermodynamics and H2 Transfer in a Methanogenic, Syntrophic Community.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20087,7 +21357,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>反应器转移改变不只传质；不是产甲烷AD，气体供给限制不等于已测内部扩散系数</t>
+          <t>代谢网络/热力学模型，不是实测细胞间距离、Deff或絮体间kf；不能将预测交换当已测物质通量</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -20104,17 +21374,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ODS-PMID32994285</t>
+          <t>ODS-PMID26498000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.1128/msystems.00323-20</t>
+          <t>10.1002/bit.25866</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Size Shapes the Active Microbiome of Methanogenic Granules, Corroborating a Biofilm Life Cycle.</t>
+          <t>Achieving complete nitrogen removal by coupling nitritation-anammox and methane-dependent denitrification: A model-based study.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20124,7 +21394,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>粒径相关不自动证明扩散限制；同时可能反映生物膜年龄、群落和底物利用差异；16S转录不是全部通量</t>
+          <t>这是模型条件下结果，不是实测通用DO最佳值；模型参数来源、校准范围待全文</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -20141,17 +21411,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ODS-PMID36374033</t>
+          <t>ODS-PMID29150508</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.1128/aem.01159-22</t>
+          <t>10.1128/aem.02186-17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Interspecies Formate Exchange Drives Syntrophic Growth of Syntrophotalea carbinolica and Methanococcus maripaludis.</t>
+          <t>Community Composition and Ultrastructure of a Nitrate-Dependent Anaerobic Methane-Oxidizing Enrichment Culture.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20161,7 +21431,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>证明载体选择与搅拌相关，不是给出了菌间距离、絮体内外通量；不将甲酸等同H2气泡</t>
+          <t>电子断层方法由摘要明确；本轮未读正文确认重建体积/分辨率；细胞接触功能未证，不能认定导电或气体通道</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -20178,17 +21448,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OR-8E15795B9DD4</t>
+          <t>ODS-PMID30236845</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.1016/j.jbiosc.2015.08.015</t>
+          <t>10.1016/j.scitotenv.2018.09.184</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>In situ probing of microbial activity within anammox granular biomass with microelectrodes.</t>
+          <t>Mass transfer affects reactor performance, microbial morphology, and community succession in the methane-dependent denitrification and anaerobic ammonium oxidation co-culture.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20198,7 +21468,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NH4/NO2/NO3/pH微电极，不是O2/H2/CH4测量；不能将该活性区写成AD氧穿透层</t>
+          <t>反应器转移改变不只传质；不是产甲烷AD，气体供给限制不等于已测内部扩散系数</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -20208,24 +21478,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>复用机制库</t>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OR-8E58C5BBDB53</t>
+          <t>ODS-PMID32994285</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.1128/aem.02146-14</t>
+          <t>10.1128/msystems.00323-20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stratified microbial structure and activity in sulfide- and methane-producing anaerobic sewer biofilms.</t>
+          <t>Size Shapes the Active Microbiome of Methanogenic Granules, Corroborating a Biofilm Life Cycle.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20235,7 +21505,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>微电极测量不等于测了氧；摘要尚不能确认二维切片与三维重建方式；没有氧冲击保护的独立干预</t>
+          <t>粒径相关不自动证明扩散限制；同时可能反映生物膜年龄、群落和底物利用差异；16S转录不是全部通量</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -20245,24 +21515,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>复用机制库</t>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OR-9AE95458315B</t>
+          <t>ODS-PMID35699440</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.1029/2018jg004602</t>
+          <t>10.1128/aem.00391-22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oxygen Transfer at the Sediment/Water Interface for Sediment Bed With Rough Surface</t>
+          <t>Stimulating Effect of Trichococcus flocculiformis on a Coculture of Syntrophomonas wolfei and Methanospirillum hungatei .</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20272,7 +21542,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>模型/实验拟合支持，不是颗粒内部气体传质的实测；无已核实统一kf/kLa数值</t>
+          <t>功能提高可能涉及信号调节或酶表达，不证明距离缩短导致H2/甲酸通量提高；非真三维成像</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -20282,24 +21552,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>复用机制库</t>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OR-F8559A118DBF</t>
+          <t>ODS-PMID35918706</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.1186/s12903-020-01217-0</t>
+          <t>10.1186/s40168-022-01311-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Use of an oxygen planar optode to assess the effect of high velocity microsprays on oxygen penetration in a human dental biofilms in-vitro.</t>
+          <t>Integrating metagenomic binning with flux balance analysis to unravel syntrophies in anaerobic CO 2 methanation.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20309,7 +21579,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>平面DO图不是三维体成像，宿主牙膜与AD不同；去除生物量与传质路径共变</t>
+          <t>共同出现和FBA不是物质通量/细胞间距离实测；不把名称flux balance当已经测到通量</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -20319,20 +21589,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>复用机制库</t>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R01133</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>ODS-PMID36374033</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10.1128/aem.01159-22</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Biogas purification using membrane micro-aeration: A mass transfer analysis</t>
+          <t>Interspecies Formate Exchange Drives Syntrophic Growth of Syntrophotalea carbinolica and Methanococcus maripaludis.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20342,7 +21616,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>文献参数和模型计算，非活性AD颗粒内Deff；DOI缺失不补造；模型数值尚未从全文核实</t>
+          <t>证明载体选择与搅拌相关，不是给出了菌间距离、絮体内外通量；不将甲酸等同H2气泡</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20352,24 +21626,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>复用机制库</t>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R06080</t>
+          <t>ODS-PMID38218075</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.1002/wer.1296</t>
+          <t>10.1016/j.watres.2024.121107</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sensor‐mediated granular sludge reactor for nitrogen removal and reduced aeration demand using a dilute wastewater</t>
+          <t>Management of biofilm by an innovative layer-structured membrane for membrane biofilm reactor (MBfR) to efficient methane oxidation coupled to denitrification (AME-D).</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20379,7 +21653,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>进水模拟AD出水，不等于反应器自身是产甲烷AD；局部颗粒DO未由摘要核实</t>
+          <t>不是产甲烷AD；多个性质共变，面积反应通量不是kLa或Deff，局部DO未核实</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -20389,20 +21663,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>复用机制库</t>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R08069</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>ODS-PMID39311608</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10.3791/67191</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Model-based analysis of microaeration for biogas desulfurization using a biomembrane</t>
+          <t>Agarose-Based Model Ecosystem for Cultivating Methanotrophs in a Methane-Oxygen Counter Gradient.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20412,7 +21690,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>拟合/敏感性不等于独立实测传质系数；DOI缺失留空；数值和温度待全文</t>
+          <t>方法参考，非AD原始颗粒；介质扩散条件不同，不能用琼脂代替污泥Deff</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -20422,157 +21700,885 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>复用机制库</t>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ODS-PMID40222284</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10.1016/j.wasman.2025.114792</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Facilitating anaerobic digestion of kitchen waste through diatomite-mediated spatial ecological niches construction.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>群落分级不是三维细胞坐标，电子传递/互营解释未测H2/甲酸通量；载体吸附与缓冲亦可能参与</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ODS-PMID42323140</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10.1016/j.biortech.2026.135209</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>A membrane-anchored nanoscale zero-valent iron bio-interface enhances interspecies electron transfer in anaerobic membrane bioreactors.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>未提供本轮已核实H2/甲酸物质通量/距离；电子传递研究不能自动算物质传质证据</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>复用组学关联论文候选；本专题首次处理，不改原数据工作线</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OR-1925EF467A30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10.1016/j.biortech.2023.129966</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Microbial stratification protects denitrifying anaerobic methane oxidation archaea and bacteria from external oxygen shock in membrane biofilm reactor.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>仅摘要未确认氧微剖面或因果保护；不是产甲烷AD；功能基因下降非速率</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OR-1E3E423A9EFE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10.1016/j.watres.2024.122400</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Activation of iron oxides through organic matter-induced dissolved oxygen penetration depth dynamics enhances iron-cycling driven ammonium oxidation in microaerobic granular sludge.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>无本轮已核实穿透深度值或微探针/模型具体方法；不是产甲烷AD，基因暗示不能当通量</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OR-52E6BA12BEDD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10.1007/s00449-012-0701-9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Spatial distribution and viability of nitrifying, denitrifying and ANAMMOX bacteria in biofilms of sponge media retrieved from a full-scale biological nutrient removal plant.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>空间位置不等于相同DO，非产甲烷菌；摘要FISH不自动算3D体重建</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OR-8E15795B9DD4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10.1016/j.jbiosc.2015.08.015</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>In situ probing of microbial activity within anammox granular biomass with microelectrodes.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NH4/NO2/NO3/pH微电极，不是O2/H2/CH4测量；不能将该活性区写成AD氧穿透层</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OR-8E58C5BBDB53</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10.1128/aem.02146-14</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Stratified microbial structure and activity in sulfide- and methane-producing anaerobic sewer biofilms.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>微电极测量不等于测了氧；摘要尚不能确认二维切片与三维重建方式；没有氧冲击保护的独立干预</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OR-9AE95458315B</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10.1029/2018jg004602</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Oxygen Transfer at the Sediment/Water Interface for Sediment Bed With Rough Surface</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>模型/实验拟合支持，不是颗粒内部气体传质的实测；无已核实统一kf/kLa数值</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>OR-B0B72D22FA67</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10.1016/j.envres.2021.110838</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Biofilm development in a pilot-scale gravity sewer: Physical characteristics, microstructure, and microbial communities.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>负ORP不是直接DO证明；微电极种类要分清，不把ORP剖面写为氧剖面</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OR-F8559A118DBF</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10.1186/s12903-020-01217-0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Use of an oxygen planar optode to assess the effect of high velocity microsprays on oxygen penetration in a human dental biofilms in-vitro.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>平面DO图不是三维体成像，宿主牙膜与AD不同；去除生物量与传质路径共变</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R01133</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Biogas purification using membrane micro-aeration: A mass transfer analysis</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>文献参数和模型计算，非活性AD颗粒内Deff；DOI缺失不补造；模型数值尚未从全文核实</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R05611</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10.1016/j.biortech.2019.122499</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Enhanced hydrolysis and acidification of cellulose at high loading for methane production via anaerobic digestion supplemented with high mobility nanobubble water</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>弛豫时间不是H2/CH4/O2扩散系数或气泡穿过污泥的直接证据；化学/底物效应需分开</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R06080</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10.1002/wer.1296</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sensor‐mediated granular sludge reactor for nitrogen removal and reduced aeration demand using a dilute wastewater</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>进水模拟AD出水，不等于反应器自身是产甲烷AD；局部颗粒DO未由摘要核实</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R06227</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10.1016/j.biortech.2020.124047</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Using air instead of biogas for mixing and its effect on anaerobic digestion of animal wastewater with high suspended solids</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>氧输入和对流同时改变；62.9%/37.1%的贡献分摊方法需正文核；混合时间不是Deff、kf或kLa</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R08069</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Model-based analysis of microaeration for biogas desulfurization using a biomembrane</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>拟合/敏感性不等于独立实测传质系数；DOI缺失留空；数值和温度待全文</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>R09240</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10.1595/205651323x16778518231554</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Microbubble Intensification of Bioprocessing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>综述中气相/液相扩散差异不能直接移植为活性颗粒的气体Deff；需回到原始试验</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R13280</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10.1002/cben.70046</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Microaeration Process Design, Control, and Monitoring for Biogas Desulfurization in Anaerobic Digestion</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>不能从综述给出通用ORP—DO换算、推荐设定值或控制收益；优先原始方法</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>R13832</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>10.1080/09593330.2018.1441329</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>A membrane aerated biofilm reactor for sulfide control from anaerobically treated wastewater.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>测序分层不是已核实三维成像；硫化物物种受pH影响，不能将去除率等同跨膜O2通量</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>待全文/补证</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>复用机制库</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>R13833</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10.1021/acs.est.8b00894</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Insight into the Role of Facultative Bacteria Stimulated by Microaeration in Continuous Bioreactors Converting LCFA to Methane</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>本轮依据摘要，不把ORP当DO反馈实测；生物膜相关不等于量得H2通量或特定互作</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>R13923</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10.1016/j.scitotenv.2024.172885</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nanobubble technology to enhance energy recovery from anaerobic digestion of organic solid wastes: Potential mechanisms and recent advancements</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>不是独立传质实测；气泡水、溶解气体和颗粒内扩散不能混用</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>R13944</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Oxidation-Reduction Potential-Based Micro-Aeration Control System for Anaerobic Digestion.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>获取/复用相关全文方法与图表，核实参数及具体限制</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>年/期刊/DOI尚缺；与R07202研究链的暴露频率表述不同，需核身份和前文，不当独立支持</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>待全文/补证</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>复用机制库</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
         <is>
           <t>10.1128/aem.00563-24</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Nondestructive and three-dimensional visualization by identifying elements using synchrotron radiation microscale X-ray CT reveals microbial and cavity distributions in anaerobic granular sludge</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>官方元数据核对题名/DOI、全库身份查重、取得正文/附件后再判断</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>网络403阻断；只有用户提供线索，未独立核实</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
+    <row r="38">
+      <c r="B38" t="inlineStr">
         <is>
           <t>10.1007/s00253-012-4616-9</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Interspecies distances between propionic acid degraders and methanogens in syntrophic consortia for optimal hydrogen transfer</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>官方元数据核对题名/DOI、全库身份查重、取得正文/附件后再判断</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>网络403阻断；只有用户提供线索，未独立核实</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>S03</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
+    <row r="39">
+      <c r="B39" t="inlineStr">
         <is>
           <t>10.1016/j.jenvman.2005.01.022</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Size-dependent anaerobic digestion rates of flocculated activated sludge: role of intrafloc mass transfer resistance</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>官方元数据核对题名/DOI、全库身份查重、取得正文/附件后再判断</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>网络403阻断；只有用户提供线索，未独立核实</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>S04</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
+    <row r="40">
+      <c r="B40" t="inlineStr">
         <is>
           <t>10.1002/bit.260330612</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Control of interspecies electron transfer flow during anaerobic digestion: Dynamic diffusion reaction models for hydrogen gas transfer in microbial flocs</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>官方元数据核对题名/DOI、全库身份查重、取得正文/附件后再判断</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>网络403阻断；只有用户提供线索，未独立核实</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>S05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20583,7 +22589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20719,12 +22725,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ODS-PMID18405985</t>
+          <t>ODS-PMID20559825</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Correlative light/electron microscopy for the investigation of microbial mats from Black Sea Cold Seeps.</t>
+          <t>Copper enhances the activity and salt resistance of mixed methane-oxidizing communities.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20744,12 +22750,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ODS-PMID20559825</t>
+          <t>ODS-PMID21899440</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Copper enhances the activity and salt resistance of mixed methane-oxidizing communities.</t>
+          <t>Sulfur-oxidizing chemolithotrophic proteobacteria dominate the microbiota in high arctic thermal springs on Svalbard.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20769,12 +22775,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ODS-PMID21899440</t>
+          <t>ODS-PMID22200642</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sulfur-oxidizing chemolithotrophic proteobacteria dominate the microbiota in high arctic thermal springs on Svalbard.</t>
+          <t>Vertical profiles of abundance and potential activity of methane-oxidizing bacteria in sediment of Lake Biwa, Japan.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20794,12 +22800,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ODS-PMID22200642</t>
+          <t>ODS-PMID23143533</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vertical profiles of abundance and potential activity of methane-oxidizing bacteria in sediment of Lake Biwa, Japan.</t>
+          <t>Co-digestion of manure and whey for in situ biogas upgrading by the addition of H(2): process performance and microbial insights.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20819,12 +22825,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ODS-PMID23143533</t>
+          <t>ODS-PMID23435898</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Co-digestion of manure and whey for in situ biogas upgrading by the addition of H(2): process performance and microbial insights.</t>
+          <t>Activated zeolite--suitable carriers for microorganisms in anaerobic digestion processes?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20844,12 +22850,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ODS-PMID23435898</t>
+          <t>ODS-PMID23446836</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Activated zeolite--suitable carriers for microorganisms in anaerobic digestion processes?</t>
+          <t>Archaeal and anaerobic methane oxidizer communities in the Sonora Margin cold seeps, Guaymas Basin (Gulf of California).</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20869,12 +22875,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ODS-PMID23446836</t>
+          <t>ODS-PMID23843725</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Archaeal and anaerobic methane oxidizer communities in the Sonora Margin cold seeps, Guaymas Basin (Gulf of California).</t>
+          <t>Deposition of biogenic iron minerals in a methane oxidizing microbial mat.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20894,12 +22900,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ODS-PMID23843725</t>
+          <t>ODS-PMID24112684</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deposition of biogenic iron minerals in a methane oxidizing microbial mat.</t>
+          <t>Microbial community structure and functioning in marine sediments associated with diffuse hydrothermal venting assessed by integrated meta-omics.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20919,12 +22925,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ODS-PMID24112684</t>
+          <t>ODS-PMID24145422</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Microbial community structure and functioning in marine sediments associated with diffuse hydrothermal venting assessed by integrated meta-omics.</t>
+          <t>Cyclic 100-ka (glacial-interglacial) migration of subseafloor redox zonation on the Peruvian shelf.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20944,12 +22950,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ODS-PMID24145422</t>
+          <t>ODS-PMID24880628</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyclic 100-ka (glacial-interglacial) migration of subseafloor redox zonation on the Peruvian shelf.</t>
+          <t>Cultivation of nitrite-dependent anaerobic methane-oxidizing bacteria: impact of reactor configuration.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20969,12 +22975,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ODS-PMID24880628</t>
+          <t>ODS-PMID24901501</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cultivation of nitrite-dependent anaerobic methane-oxidizing bacteria: impact of reactor configuration.</t>
+          <t>Magnetite particles triggering a faster and more robust syntrophic pathway of methanogenic propionate degradation.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20994,12 +23000,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ODS-PMID24901501</t>
+          <t>ODS-PMID24946864</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Magnetite particles triggering a faster and more robust syntrophic pathway of methanogenic propionate degradation.</t>
+          <t>Hydrolysis, acidification and methanogenesis during low-temperature anaerobic digestion of dilute dairy wastewater in an inverted fluidised bioreactor.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -21019,12 +23025,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ODS-PMID24946864</t>
+          <t>ODS-PMID25393146</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hydrolysis, acidification and methanogenesis during low-temperature anaerobic digestion of dilute dairy wastewater in an inverted fluidised bioreactor.</t>
+          <t>Stratified community responses to methane and sulfate supplies in mud volcano deposits: insights from an in vitro experiment.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -21044,12 +23050,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ODS-PMID25393146</t>
+          <t>ODS-PMID25462775</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stratified community responses to methane and sulfate supplies in mud volcano deposits: insights from an in vitro experiment.</t>
+          <t>Application of eco-compatible biochar in anaerobic digestion to relieve acid stress and promote the selective colonization of functional microbes.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -21069,12 +23075,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ODS-PMID25462775</t>
+          <t>ODS-PMID25755930</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Application of eco-compatible biochar in anaerobic digestion to relieve acid stress and promote the selective colonization of functional microbes.</t>
+          <t>Oxygen availability is a major factor in determining the composition of microbial communities involved in methane oxidation.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -21094,12 +23100,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ODS-PMID25755930</t>
+          <t>ODS-PMID26079858</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oxygen availability is a major factor in determining the composition of microbial communities involved in methane oxidation.</t>
+          <t>Selective Enrichment Establishes a Stable Performing Community for Microbial Electrosynthesis of Acetate from CO₂.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -21119,12 +23125,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ODS-PMID26079858</t>
+          <t>ODS-PMID26081483</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Selective Enrichment Establishes a Stable Performing Community for Microbial Electrosynthesis of Acetate from CO₂.</t>
+          <t>Crustal fluid and ash alteration impacts on the biosphere of Shikoku Basin sediments, Nankai Trough, Japan.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -21144,12 +23150,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ODS-PMID26081483</t>
+          <t>ODS-PMID26599000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Crustal fluid and ash alteration impacts on the biosphere of Shikoku Basin sediments, Nankai Trough, Japan.</t>
+          <t>Microbial Response to Experimentally Controlled Redox Transitions at the Sediment Water Interface.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -21169,12 +23175,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ODS-PMID26498000</t>
+          <t>ODS-PMID26694756</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Achieving complete nitrogen removal by coupling nitritation-anammox and methane-dependent denitrification: A model-based study.</t>
+          <t>Analysis of the Microbial Community in an Acidic Hollow-Fiber Membrane Biofilm Reactor (Hf-MBfR) Used for the Biological Conversion of Carbon Dioxide to Methane.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -21194,12 +23200,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ODS-PMID26599000</t>
+          <t>ODS-PMID26712547</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Microbial Response to Experimentally Controlled Redox Transitions at the Sediment Water Interface.</t>
+          <t>Long-Term Enrichment on Cellulose or Xylan Causes Functional and Taxonomic Convergence of Microbial Communities from Anaerobic Digesters.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -21219,12 +23225,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ODS-PMID26694756</t>
+          <t>ODS-PMID26964364</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Analysis of the Microbial Community in an Acidic Hollow-Fiber Membrane Biofilm Reactor (Hf-MBfR) Used for the Biological Conversion of Carbon Dioxide to Methane.</t>
+          <t>[Microbial Processes and Genesis of Methane Gas Jets in the Coastal Areas of the Crimea Peninsula].</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -21244,12 +23250,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ODS-PMID26712547</t>
+          <t>ODS-PMID27065954</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Long-Term Enrichment on Cellulose or Xylan Causes Functional and Taxonomic Convergence of Microbial Communities from Anaerobic Digesters.</t>
+          <t>Methane Seep in Shallow-Water Permeable Sediment Harbors High Diversity of Anaerobic Methanotrophic Communities, Elba, Italy.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -21269,12 +23275,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ODS-PMID26964364</t>
+          <t>ODS-PMID27349520</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[Microbial Processes and Genesis of Methane Gas Jets in the Coastal Areas of the Crimea Peninsula].</t>
+          <t>Hardwiring microbes via direct interspecies electron transfer: mechanisms and applications.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -21294,12 +23300,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ODS-PMID27065954</t>
+          <t>ODS-PMID27931939</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Methane Seep in Shallow-Water Permeable Sediment Harbors High Diversity of Anaerobic Methanotrophic Communities, Elba, Italy.</t>
+          <t>Ex-situ biogas upgrading and enhancement in different reactor systems.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -21319,12 +23325,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ODS-PMID27349520</t>
+          <t>ODS-PMID28235661</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hardwiring microbes via direct interspecies electron transfer: mechanisms and applications.</t>
+          <t>Hollow fiber membrane bioreactor affects microbial community and morphology of the DAMO and Anammox co-culture system.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21344,12 +23350,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ODS-PMID27931939</t>
+          <t>ODS-PMID29028292</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ex-situ biogas upgrading and enhancement in different reactor systems.</t>
+          <t>Dynamics of soil biogeochemical gas emissions shaped by remolded aggregate sizes and carbon configurations under hydration cycles.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -21369,12 +23375,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ODS-PMID28235661</t>
+          <t>ODS-PMID29876073</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hollow fiber membrane bioreactor affects microbial community and morphology of the DAMO and Anammox co-culture system.</t>
+          <t>Long-term nutrient addition increases respiration and nitrous oxide emissions in a New England salt marsh.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21394,12 +23400,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ODS-PMID29028292</t>
+          <t>ODS-PMID30401770</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dynamics of soil biogeochemical gas emissions shaped by remolded aggregate sizes and carbon configurations under hydration cycles.</t>
+          <t>Members of the Genus Methylobacter Are Inferred To Account for the Majority of Aerobic Methane Oxidation in Oxic Soils from a Freshwater Wetland.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -21419,12 +23425,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ODS-PMID29150508</t>
+          <t>ODS-PMID30772540</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Community Composition and Ultrastructure of a Nitrate-Dependent Anaerobic Methane-Oxidizing Enrichment Culture.</t>
+          <t>Microbial metabolic strategies for overcoming low-oxygen in naturalized freshwater reservoirs surrounding the Athabasca Oil Sands: A proxy for End-Pit Lakes?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -21444,12 +23450,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ODS-PMID29876073</t>
+          <t>ODS-PMID30804909</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Long-term nutrient addition increases respiration and nitrous oxide emissions in a New England salt marsh.</t>
+          <t>Changes in Carbon Oxidation State of Metagenomes Along Geochemical Redox Gradients.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -21469,12 +23475,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ODS-PMID30401770</t>
+          <t>ODS-PMID31059873</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Members of the Genus Methylobacter Are Inferred To Account for the Majority of Aerobic Methane Oxidation in Oxic Soils from a Freshwater Wetland.</t>
+          <t>Potential of direct interspecies electron transfer in synergetic enhancement of methanogenesis and sulfate removal in an up-flow anaerobic sludge blanket reactor with magnetite.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -21494,12 +23500,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ODS-PMID30772540</t>
+          <t>ODS-PMID31278352</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Microbial metabolic strategies for overcoming low-oxygen in naturalized freshwater reservoirs surrounding the Athabasca Oil Sands: A proxy for End-Pit Lakes?</t>
+          <t>Methane-fuelled biofilms predominantly composed of methanotrophic ANME-1 in Arctic gas hydrate-related sediments.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -21519,12 +23525,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ODS-PMID30804909</t>
+          <t>ODS-PMID32038509</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Changes in Carbon Oxidation State of Metagenomes Along Geochemical Redox Gradients.</t>
+          <t>A Methanogenic Consortium Was Active and Exhibited Long-Term Survival in an Extremely Acidified Thermophilic Bioreactor.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -21544,12 +23550,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ODS-PMID31059873</t>
+          <t>ODS-PMID32563694</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Potential of direct interspecies electron transfer in synergetic enhancement of methanogenesis and sulfate removal in an up-flow anaerobic sludge blanket reactor with magnetite.</t>
+          <t>New bacterial and archaeal lineages discovered in organic rich sediments of a large tropical Bay.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -21569,12 +23575,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ODS-PMID31278352</t>
+          <t>ODS-PMID32957047</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Methane-fuelled biofilms predominantly composed of methanotrophic ANME-1 in Arctic gas hydrate-related sediments.</t>
+          <t>Effect of proton pump inhibitor on microbial community, function, and kinetics in anaerobic digestion with ammonia stress.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -21594,12 +23600,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ODS-PMID32038509</t>
+          <t>ODS-PMID33187999</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A Methanogenic Consortium Was Active and Exhibited Long-Term Survival in an Extremely Acidified Thermophilic Bioreactor.</t>
+          <t>Organohalide-Respiring Bacteria at the Heart of Anaerobic Metabolism in Arctic Wet Tundra Soils.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -21619,12 +23625,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ODS-PMID32563694</t>
+          <t>ODS-PMID33295079</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New bacterial and archaeal lineages discovered in organic rich sediments of a large tropical Bay.</t>
+          <t>Sulfide alters microbial functional potential in a methane and nitrogen cycling biofilm reactor.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -21644,12 +23650,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ODS-PMID32957047</t>
+          <t>ODS-PMID34132588</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Effect of proton pump inhibitor on microbial community, function, and kinetics in anaerobic digestion with ammonia stress.</t>
+          <t>The Oligosaccharyltransferase AglB Supports Surface-Associated Growth and Iron Oxidation in Methanococcus maripaludis.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -21669,12 +23675,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ODS-PMID33187999</t>
+          <t>ODS-PMID34183781</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Organohalide-Respiring Bacteria at the Heart of Anaerobic Metabolism in Arctic Wet Tundra Soils.</t>
+          <t>Methane-dependent selenate reduction by a bacterial consortium.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -21694,12 +23700,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ODS-PMID33295079</t>
+          <t>ODS-PMID34335545</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sulfide alters microbial functional potential in a methane and nitrogen cycling biofilm reactor.</t>
+          <t>Microbial Communities of Hydrothermal Guaymas Basin Surficial Sediment Profiled at 2 Millimeter-Scale Resolution.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -21719,12 +23725,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ODS-PMID34132588</t>
+          <t>ODS-PMID35661512</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>The Oligosaccharyltransferase AglB Supports Surface-Associated Growth and Iron Oxidation in Methanococcus maripaludis.</t>
+          <t>A novel green composite conductive material enhancing anaerobic digestion of waste activated sludge via improving electron transfer and metabolic activity.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -21744,12 +23750,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ODS-PMID34183781</t>
+          <t>ODS-PMID35724480</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Methane-dependent selenate reduction by a bacterial consortium.</t>
+          <t>Polyhydroxyalkanoate-driven current generation via acetate by an anaerobic methanotrophic consortium.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -21769,12 +23775,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ODS-PMID34335545</t>
+          <t>ODS-PMID36183874</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Microbial Communities of Hydrothermal Guaymas Basin Surficial Sediment Profiled at 2 Millimeter-Scale Resolution.</t>
+          <t>Sediment nitrogen contents controlled by microbial community in a eutrophic tributary in Three Gorges Reservoir, China.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -21794,12 +23800,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ODS-PMID35661512</t>
+          <t>ODS-PMID36694212</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A novel green composite conductive material enhancing anaerobic digestion of waste activated sludge via improving electron transfer and metabolic activity.</t>
+          <t>Variable impact of geochemical gradients on the functional potential of bacteria, archaea, and phages from the permanently stratified Lac Pavin.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -21819,12 +23825,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ODS-PMID35699440</t>
+          <t>ODS-PMID37105103</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stimulating Effect of Trichococcus flocculiformis on a Coculture of Syntrophomonas wolfei and Methanospirillum hungatei .</t>
+          <t>Enhancement of nitrogen removal in coupling Anammox and DAMO via Fe-modiﬁed granular activated carbon.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -21844,12 +23850,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ODS-PMID35724480</t>
+          <t>ODS-PMID37187373</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Polyhydroxyalkanoate-driven current generation via acetate by an anaerobic methanotrophic consortium.</t>
+          <t>Multi-parameter control-based operation strategy for mainstream deammonification in an integrated anaerobic biofilm reactor-step feed MBR.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -21869,12 +23875,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ODS-PMID35918706</t>
+          <t>ODS-PMID38128741</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Integrating metagenomic binning with flux balance analysis to unravel syntrophies in anaerobic CO 2 methanation.</t>
+          <t>Methane diffusion affects characteristics of benthic communities in and around microbial mat-covered sediments in the northeastern Japan sea.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -21894,12 +23900,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ODS-PMID36183874</t>
+          <t>ODS-PMID38631226</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sediment nitrogen contents controlled by microbial community in a eutrophic tributary in Three Gorges Reservoir, China.</t>
+          <t>Active microbial communities facilitate carbon turnover in brine pools found in the deep Southeastern Mediterranean Sea.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -21919,12 +23925,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ODS-PMID36694212</t>
+          <t>ODS-PMID38876277</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Variable impact of geochemical gradients on the functional potential of bacteria, archaea, and phages from the permanently stratified Lac Pavin.</t>
+          <t>Deciphering Fe@C amendment on long-term anaerobic digestion of sulfate and propionate rich wastewater: Driving microbial community succession and propionate metabolism.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -21944,12 +23950,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ODS-PMID37105103</t>
+          <t>ODS-PMID39110235</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Enhancement of nitrogen removal in coupling Anammox and DAMO via Fe-modiﬁed granular activated carbon.</t>
+          <t>Impact of additives on syntrophic propionate and acetate enrichments under high-ammonia conditions.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -21969,12 +23975,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ODS-PMID37187373</t>
+          <t>ODS-PMID39411197</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Multi-parameter control-based operation strategy for mainstream deammonification in an integrated anaerobic biofilm reactor-step feed MBR.</t>
+          <t>Metagenomic and -transcriptomic analyses of microbial nitrogen transformation potential, and gene expression in Swiss lake sediments.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -21994,12 +24000,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ODS-PMID38128741</t>
+          <t>ODS-PMID39699221</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Methane diffusion affects characteristics of benthic communities in and around microbial mat-covered sediments in the northeastern Japan sea.</t>
+          <t>Extracellular electron transfer genes expressed by candidate flocking bacteria in cable bacteria sediment.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -22019,12 +24025,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ODS-PMID38218075</t>
+          <t>ODS-PMID39980692</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Management of biofilm by an innovative layer-structured membrane for membrane biofilm reactor (MBfR) to efficient methane oxidation coupled to denitrification (AME-D).</t>
+          <t>Drivers of methane-cycling archaeal abundances, community structure, and catabolic pathways in continental margin sediments.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -22044,12 +24050,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ODS-PMID38631226</t>
+          <t>ODS-PMID39983491</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Active microbial communities facilitate carbon turnover in brine pools found in the deep Southeastern Mediterranean Sea.</t>
+          <t>Microbial dynamics and CO consumption enhancement via co-digestion with carbohydrate-rich synthetic wastewater.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -22069,12 +24075,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ODS-PMID38876277</t>
+          <t>ODS-PMID40020369</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Deciphering Fe@C amendment on long-term anaerobic digestion of sulfate and propionate rich wastewater: Driving microbial community succession and propionate metabolism.</t>
+          <t>Long-term effects of food waste on erosion resistance and production of methane and sulfide in sewer sediments: New insights into extracellular polymeric substances and genetic response mechanisms.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -22094,12 +24100,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ODS-PMID39110235</t>
+          <t>ODS-PMID40024576</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Impact of additives on syntrophic propionate and acetate enrichments under high-ammonia conditions.</t>
+          <t>Enhancing denitrifying anaerobic methane oxidation for nitrogen removal with low-temperature biochar.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -22119,12 +24125,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ODS-PMID39311608</t>
+          <t>ODS-PMID40153957</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Agarose-Based Model Ecosystem for Cultivating Methanotrophs in a Methane-Oxygen Counter Gradient.</t>
+          <t>Methane cycling in typical emerging proglacial lakes on the Tibetan Plateau: Insights into the metabolic mechanisms mediated by microorganisms.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -22144,12 +24150,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ODS-PMID39411197</t>
+          <t>ODS-PMID40268215</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Metagenomic and -transcriptomic analyses of microbial nitrogen transformation potential, and gene expression in Swiss lake sediments.</t>
+          <t>Synergy of multi-enzyme pretreatment and Paraclostridium benzoelyticum bioaugmentation: A dual strategy for enhancing methane production in dry anaerobic digestion of kitchen waste.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -22169,12 +24175,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ODS-PMID39699221</t>
+          <t>ODS-PMID40897101</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Extracellular electron transfer genes expressed by candidate flocking bacteria in cable bacteria sediment.</t>
+          <t>Increased snowpack enhances ecological functions of cold-region constructed wetlands via plant-microbe interactions.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -22194,12 +24200,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ODS-PMID39980692</t>
+          <t>ODS-PMID40923736</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Drivers of methane-cycling archaeal abundances, community structure, and catabolic pathways in continental margin sediments.</t>
+          <t>Diagnosis of Pulmonary Actinomycosis Caused by Actinomyces graevenitzii: a Case Series of Three Patients.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -22219,12 +24225,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ODS-PMID39983491</t>
+          <t>ODS-PMID41175758</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Microbial dynamics and CO consumption enhancement via co-digestion with carbohydrate-rich synthetic wastewater.</t>
+          <t>Unraveling synergistic mechanisms of bioelectrocatalytic methane enhancement and membrane fouling alleviation via composite anodic membrane assembly in anaerobic bioreactor treating purified terephthalic acid wastewater.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -22244,12 +24250,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ODS-PMID40020369</t>
+          <t>ODS-PMID41224035</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Long-term effects of food waste on erosion resistance and production of methane and sulfide in sewer sediments: New insights into extracellular polymeric substances and genetic response mechanisms.</t>
+          <t>Microbiota ecology upon moderate concentrations of total ammoniacal nitrogen enhances methane production of anaerobic membrane bioreactor.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -22269,12 +24275,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ODS-PMID40024576</t>
+          <t>ODS-PMID41273495</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Enhancing denitrifying anaerobic methane oxidation for nitrogen removal with low-temperature biochar.</t>
+          <t>GO/iron series enhance performance of anaerobic system for treatment of sulfate-containing organic wastewater.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -22294,12 +24300,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ODS-PMID40153957</t>
+          <t>ODS-PMID41421680</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Methane cycling in typical emerging proglacial lakes on the Tibetan Plateau: Insights into the metabolic mechanisms mediated by microorganisms.</t>
+          <t>Synergistic enhancement of biomethanation integrating H 2 injection with external CO 2 in thermophilic anaerobic digestion of sewage sludge.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -22319,12 +24325,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ODS-PMID40222284</t>
+          <t>ODS-PMID41486817</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Facilitating anaerobic digestion of kitchen waste through diatomite-mediated spatial ecological niches construction.</t>
+          <t>Millimetre-Scale Stratification of Microbial Communities in Hydrothermal Sediments.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -22344,12 +24350,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ODS-PMID40268215</t>
+          <t>ODS-PMID41574941</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Synergy of multi-enzyme pretreatment and Paraclostridium benzoelyticum bioaugmentation: A dual strategy for enhancing methane production in dry anaerobic digestion of kitchen waste.</t>
+          <t>Seasons and vertical dynamics influence community composition in a flooded and abandoned mica mine.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -22369,12 +24375,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ODS-PMID40897101</t>
+          <t>ODS-PMID41783502</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Increased snowpack enhances ecological functions of cold-region constructed wetlands via plant-microbe interactions.</t>
+          <t>Bacteria-archaea metabolic complementarity as a driver of ecosystem functioning in Chinese coastal sediments.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -22394,12 +24400,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ODS-PMID40923736</t>
+          <t>ODS-PMID41987322</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Diagnosis of Pulmonary Actinomycosis Caused by Actinomyces graevenitzii: a Case Series of Three Patients.</t>
+          <t>Evidence for cable bacteria inhabiting deep in anoxic sediment reveals a novel ecological niche.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -22419,12 +24425,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ODS-PMID41175758</t>
+          <t>ODS-PMID42101523</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Unraveling synergistic mechanisms of bioelectrocatalytic methane enhancement and membrane fouling alleviation via composite anodic membrane assembly in anaerobic bioreactor treating purified terephthalic acid wastewater.</t>
+          <t>Insights into the critical processes of methane biogeochemical cycling in inland freshwater ecosystems: a systematic review.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -22444,12 +24450,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ODS-PMID41224035</t>
+          <t>ODS-PMID42225162</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Microbiota ecology upon moderate concentrations of total ammoniacal nitrogen enhances methane production of anaerobic membrane bioreactor.</t>
+          <t>A stress-response-recovery framework integrating microbial life-history strategies for stressed anaerobic digestion.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -22469,12 +24475,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ODS-PMID41273495</t>
+          <t>ODS-PMID42413272</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GO/iron series enhance performance of anaerobic system for treatment of sulfate-containing organic wastewater.</t>
+          <t>Overcoming thermodynamic limitations on anaerobic methanogenesis via DSF/c-di-GMP enhanced indirect interspecies electron transfer.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -22494,12 +24500,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ODS-PMID41421680</t>
+          <t>ODS-PMID42478355</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Synergistic enhancement of biomethanation integrating H 2 injection with external CO 2 in thermophilic anaerobic digestion of sewage sludge.</t>
+          <t>Microbial Reduction of Methane Emissions from High-Altitude Thermokarst Lakes.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -22519,12 +24525,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ODS-PMID41486817</t>
+          <t>ODS-PMID42531877</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Millimetre-Scale Stratification of Microbial Communities in Hydrothermal Sediments.</t>
+          <t>Decoding the metabolic synergy and extracellular electron transfer bottleneck in manganese-driven nitrogen removal: Mechanisms underlying the dominance of comammox bacteria.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -22544,12 +24550,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ODS-PMID41574941</t>
+          <t>ODS-PMID42567290</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seasons and vertical dynamics influence community composition in a flooded and abandoned mica mine.</t>
+          <t>Hydrodynamic control of oxygen intrusion and shear stabilizes functional zonation for nitrogen removal in an integrated UASB.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -22569,12 +24575,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ODS-PMID41783502</t>
+          <t>ODS-PMID42916424</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bacteria-archaea metabolic complementarity as a driver of ecosystem functioning in Chinese coastal sediments.</t>
+          <t>Drivers of Seasonal Variations of Greenhouse Gas Fluxes from Sediment-Water and Water-Atmosphere Interfaces in Different Fish Culture Ponds.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -22594,12 +24600,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ODS-PMID41987322</t>
+          <t>OR-0DA1B168B9E7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Evidence for cable bacteria inhabiting deep in anoxic sediment reveals a novel ecological niche.</t>
+          <t>GAL08, an Uncultivated Group of Acidobacteria, Is a Dominant Bacterial Clade in a Neutral Hot Spring</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -22619,12 +24625,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ODS-PMID42101523</t>
+          <t>OR-1270182F08D1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Insights into the critical processes of methane biogeochemical cycling in inland freshwater ecosystems: a systematic review.</t>
+          <t>Alginate-based biofilm-assisted encapsulation of a Co-culture of Bifidobacterium longum DSM20219 and Bacillus subtilis SOM8 enhances resistance to gastrointestinal stress.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -22644,12 +24650,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ODS-PMID42225162</t>
+          <t>OR-13330FD2DB3C</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A stress-response-recovery framework integrating microbial life-history strategies for stressed anaerobic digestion.</t>
+          <t>Photocatalyst-driven microalgal-bacterial symbiosis enables organic carbon-free and energy-efficient nitrogen removal in a pilot-scale wastewater treatment.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -22669,12 +24675,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ODS-PMID42323140</t>
+          <t>OR-14B9C58DBFD7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A membrane-anchored nanoscale zero-valent iron bio-interface enhances interspecies electron transfer in anaerobic membrane bioreactors.</t>
+          <t>Fe(III) oxides protect fermenter-methanogen syntrophy against interruption by elemental sulfur via stiffening of Fe(II) sulfides produced by sulfur respiration.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -22694,12 +24700,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ODS-PMID42413272</t>
+          <t>OR-17F6AED9522E</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Overcoming thermodynamic limitations on anaerobic methanogenesis via DSF/c-di-GMP enhanced indirect interspecies electron transfer.</t>
+          <t>Chlorate Specifically Targets Oxidant-Starved, Antibiotic-Tolerant Populations of Pseudomonas aeruginosa Biofilms.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -22719,12 +24725,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ODS-PMID42478355</t>
+          <t>OR-18F0D119B7B6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Microbial Reduction of Methane Emissions from High-Altitude Thermokarst Lakes.</t>
+          <t>A novel standalone microfluidic device for local control of oxygen tension for intestinal-bacteria interactions.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -22744,12 +24750,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ODS-PMID42531877</t>
+          <t>OR-1C07DB143232</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Decoding the metabolic synergy and extracellular electron transfer bottleneck in manganese-driven nitrogen removal: Mechanisms underlying the dominance of comammox bacteria.</t>
+          <t>Interesting anaerobes in the environment</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -22769,12 +24775,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ODS-PMID42567290</t>
+          <t>OR-1F091C75F6F3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hydrodynamic control of oxygen intrusion and shear stabilizes functional zonation for nitrogen removal in an integrated UASB.</t>
+          <t>The effect of the COD: N ratio on mainstream deammonification in an integrated fixed-film activated sludge sequencing batch reactor.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -22794,12 +24800,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ODS-PMID42916424</t>
+          <t>OR-2205F2FD0EB7</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Drivers of Seasonal Variations of Greenhouse Gas Fluxes from Sediment-Water and Water-Atmosphere Interfaces in Different Fish Culture Ponds.</t>
+          <t>Transcriptomics Uncovers the Response of Anammox Bacteria to Dissolved Oxygen Inhibition and the Subsequent Recovery Mechanism.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -22819,12 +24825,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OR-0DA1B168B9E7</t>
+          <t>OR-25414A3F7171</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GAL08, an Uncultivated Group of Acidobacteria, Is a Dominant Bacterial Clade in a Neutral Hot Spring</t>
+          <t>Effects of organic matter in livestock manure digester liquid on microbial community structure and in situ activity of anammox granules.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -22844,12 +24850,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OR-1270182F08D1</t>
+          <t>OR-280B59EA9E89</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Alginate-based biofilm-assisted encapsulation of a Co-culture of Bifidobacterium longum DSM20219 and Bacillus subtilis SOM8 enhances resistance to gastrointestinal stress.</t>
+          <t>Aerobic Vitamin B12 Biosynthesis Is Essential for Pseudomonas aeruginosa Class II Ribonucleotide Reductase Activity During Planktonic and Biofilm Growth.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -22869,12 +24875,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OR-13330FD2DB3C</t>
+          <t>OR-2ABF1479FD62</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Photocatalyst-driven microalgal-bacterial symbiosis enables organic carbon-free and energy-efficient nitrogen removal in a pilot-scale wastewater treatment.</t>
+          <t>Individualizing Basketball-Specific Interval Training Using Anaerobic Speed Reserve: Effects on Physiological and Hormonal Adaptations.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -22894,12 +24900,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OR-14B9C58DBFD7</t>
+          <t>OR-2B20BAEA8F73</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fe(III) oxides protect fermenter-methanogen syntrophy against interruption by elemental sulfur via stiffening of Fe(II) sulfides produced by sulfur respiration.</t>
+          <t>Intermittent aeration enhances biological nitrogen removal from low C/N synthetic domestic wastewater.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -22919,12 +24925,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OR-17F6AED9522E</t>
+          <t>OR-2BB4A49BEF0D</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chlorate Specifically Targets Oxidant-Starved, Antibiotic-Tolerant Populations of Pseudomonas aeruginosa Biofilms.</t>
+          <t>Anammox bacteria adapt to long-term light irradiation in photogranules.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -22944,12 +24950,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OR-18F0D119B7B6</t>
+          <t>OR-2F8ECD7A40A8</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A novel standalone microfluidic device for local control of oxygen tension for intestinal-bacteria interactions.</t>
+          <t>Impact of oxygen injection on CH4 and N2O emissions from rising main sewers.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -22969,12 +24975,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OR-1925EF467A30</t>
+          <t>OR-30D9E6180F40</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Microbial stratification protects denitrifying anaerobic methane oxidation archaea and bacteria from external oxygen shock in membrane biofilm reactor.</t>
+          <t>Trichloroethylene detoxification in low-permeability soil via electrokinetic-enhanced bioremediation technology: Long-term feasibility and spatial-temporal patterns.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -22994,12 +25000,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OR-1C07DB143232</t>
+          <t>OR-338653210941</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Interesting anaerobes in the environment</t>
+          <t>Adaptation of Akkermansia muciniphila to the Oxic-Anoxic Interface of the Mucus Layer.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -23019,12 +25025,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OR-1E3E423A9EFE</t>
+          <t>OR-33B510329570</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Activation of iron oxides through organic matter-induced dissolved oxygen penetration depth dynamics enhances iron-cycling driven ammonium oxidation in microaerobic granular sludge.</t>
+          <t>Comparison of short-term dosing ferrous ion and nanoscale zero-valent iron for rapid recovery of anammox activity from dissolved oxygen inhibition.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -23044,12 +25050,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OR-1F091C75F6F3</t>
+          <t>OR-3AD765670E11</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The effect of the COD: N ratio on mainstream deammonification in an integrated fixed-film activated sludge sequencing batch reactor.</t>
+          <t>Microbial functional genes are driven by gradients in sediment stoichiometry, oxygen, and salinity across the Baltic benthic ecosystem</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -23069,12 +25075,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OR-2205F2FD0EB7</t>
+          <t>OR-3C0E505B4E2A</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Transcriptomics Uncovers the Response of Anammox Bacteria to Dissolved Oxygen Inhibition and the Subsequent Recovery Mechanism.</t>
+          <t>Evaluation of the impact of dissolved oxygen concentration on biofilm microbial community in sequencing batch biofilm reactor.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -23094,12 +25100,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OR-25414A3F7171</t>
+          <t>OR-40D2DF84C097</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Effects of organic matter in livestock manure digester liquid on microbial community structure and in situ activity of anammox granules.</t>
+          <t>Influence of 20-year organic and inorganic fertilization on organic carbon accumulation and microbial community structure of aggregates in an intensively cultivated sandy loam soil.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -23119,12 +25125,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OR-280B59EA9E89</t>
+          <t>OR-44AA178A2EA7</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Aerobic Vitamin B12 Biosynthesis Is Essential for Pseudomonas aeruginosa Class II Ribonucleotide Reductase Activity During Planktonic and Biofilm Growth.</t>
+          <t>Simultaneous enhancement of copper removal and power production using a sediment microbial fuel cell with oxygen separation membranes</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -23144,12 +25150,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OR-2ABF1479FD62</t>
+          <t>OR-48AC15A87A33</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Individualizing Basketball-Specific Interval Training Using Anaerobic Speed Reserve: Effects on Physiological and Hormonal Adaptations.</t>
+          <t>New strategy for integration of anaerobic side-stream reactor with mainstream B-stage nitritation for short-cut nitrogen removal with granulation.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -23169,12 +25175,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OR-2B20BAEA8F73</t>
+          <t>OR-4C2FA5E5F635</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Intermittent aeration enhances biological nitrogen removal from low C/N synthetic domestic wastewater.</t>
+          <t>Aerobic and anaerobic nitrogen transformation processes in N2-fixing cyanobacterial aggregates.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -23194,12 +25200,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OR-2BB4A49BEF0D</t>
+          <t>OR-53E5B6837830</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Anammox bacteria adapt to long-term light irradiation in photogranules.</t>
+          <t>The adaptability of Pseudomonas aeruginosa biofilm in oxygen-limited environments.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -23219,12 +25225,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OR-2F8ECD7A40A8</t>
+          <t>OR-54444D2CBFD4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Impact of oxygen injection on CH4 and N2O emissions from rising main sewers.</t>
+          <t>Interface-dependent V. parahaemolyticus biofilm under varying temperatures, media, and oxygen conditions: implications for seafood safety.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -23244,12 +25250,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OR-30D9E6180F40</t>
+          <t>OR-580C4B81E83F</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Trichloroethylene detoxification in low-permeability soil via electrokinetic-enhanced bioremediation technology: Long-term feasibility and spatial-temporal patterns.</t>
+          <t>Sediment Disturbance Negatively Impacts Methanogen Abundance but Has Variable Effects on Total Methane Emissions.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -23269,12 +25275,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OR-338653210941</t>
+          <t>OR-5F33AA9038E0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Adaptation of Akkermansia muciniphila to the Oxic-Anoxic Interface of the Mucus Layer.</t>
+          <t>[Clinical study on the characteristics of exercise pathophysiological in patients with severe heart failure].</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -23294,12 +25300,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>OR-33B510329570</t>
+          <t>OR-62193AEC83E9</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Comparison of short-term dosing ferrous ion and nanoscale zero-valent iron for rapid recovery of anammox activity from dissolved oxygen inhibition.</t>
+          <t>Achieving nitrogen removal in the integrated upper fixed-biofilm activated sludge reactor without recirculation: Differential protein and metagenomic analysis.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -23319,12 +25325,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OR-3AD765670E11</t>
+          <t>OR-6616F8EC469F</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Microbial functional genes are driven by gradients in sediment stoichiometry, oxygen, and salinity across the Baltic benthic ecosystem</t>
+          <t>Spontaneous mainstream anammox in a full-scale wastewater treatment plant with hybrid sludge retention time in a temperate zone of China.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -23344,12 +25350,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OR-3C0E505B4E2A</t>
+          <t>OR-698FFA4847F7</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Evaluation of the impact of dissolved oxygen concentration on biofilm microbial community in sequencing batch biofilm reactor.</t>
+          <t>A photocatalytic Anammox@LC-COF biohybrid overcomes oxidative stress defense for resilient nitrogen removal.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -23369,12 +25375,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OR-40D2DF84C097</t>
+          <t>OR-69DA054B08A8</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Influence of 20-year organic and inorganic fertilization on organic carbon accumulation and microbial community structure of aggregates in an intensively cultivated sandy loam soil.</t>
+          <t>Facilitated extracellular electron transfer of Shewanella loihica PV-4 by antimony-doped tin oxide nanoparticles as active microelectrodes.</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -23394,12 +25400,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OR-44AA178A2EA7</t>
+          <t>OR-6CAE850AD459</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Simultaneous enhancement of copper removal and power production using a sediment microbial fuel cell with oxygen separation membranes</t>
+          <t>ArnR binds a [4Fe-4S] cluster and indirectly senses anaerobicity in Corynebacteria.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -23419,12 +25425,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OR-48AC15A87A33</t>
+          <t>OR-6D00DC189CB1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New strategy for integration of anaerobic side-stream reactor with mainstream B-stage nitritation for short-cut nitrogen removal with granulation.</t>
+          <t>Development of a novel human intestinal model to elucidate the effect of anaerobic commensals on Escherichia coli infection.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -23444,12 +25450,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OR-4C2FA5E5F635</t>
+          <t>OR-6D1F6319B015</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Aerobic and anaerobic nitrogen transformation processes in N2-fixing cyanobacterial aggregates.</t>
+          <t>A novel approach for achieving high enrichment of anammox and nitrogen removal rate in municipal wastewater treatment: A pure biofilm process.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23469,12 +25475,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>OR-52E6BA12BEDD</t>
+          <t>OR-6D34644D86D9</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spatial distribution and viability of nitrifying, denitrifying and ANAMMOX bacteria in biofilms of sponge media retrieved from a full-scale biological nutrient removal plant.</t>
+          <t>A low-cost microbial fuel cell based sensor for in-situ monitoring of dissolved oxygen for over half a year.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23494,12 +25500,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OR-53E5B6837830</t>
+          <t>OR-6FAF906F2BA4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>The adaptability of Pseudomonas aeruginosa biofilm in oxygen-limited environments.</t>
+          <t>The Selenoproteome as a Dynamic Response Mechanism to Oxidative Stress in Hydrogenotrophic Methanogenic Communities.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23519,12 +25525,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OR-54444D2CBFD4</t>
+          <t>OR-77805E828A28</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Interface-dependent V. parahaemolyticus biofilm under varying temperatures, media, and oxygen conditions: implications for seafood safety.</t>
+          <t>In Situ Spectroelectrochemical Characterization Reveals Cytochrome-Mediated Electric Syntrophy in Geobacter Coculture.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23544,12 +25550,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>OR-580C4B81E83F</t>
+          <t>OR-7E9ABB53F760</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sediment Disturbance Negatively Impacts Methanogen Abundance but Has Variable Effects on Total Methane Emissions.</t>
+          <t>Combination of upflow anaerobic sludge blanket (UASB) reactor and partial nitritation/anammox moving bed biofilm reactor (MBBR) for municipal wastewater treatment.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23569,12 +25575,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OR-5F33AA9038E0</t>
+          <t>OR-7F64C2887E13</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>[Clinical study on the characteristics of exercise pathophysiological in patients with severe heart failure].</t>
+          <t>Pseudomonas aeruginosa Exhibits Deficient Biofilm Formation in the Absence of Class II and III Ribonucleotide Reductases Due to Hindered Anaerobic Growth.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -23594,12 +25600,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OR-62193AEC83E9</t>
+          <t>OR-81B738B20350</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Achieving nitrogen removal in the integrated upper fixed-biofilm activated sludge reactor without recirculation: Differential protein and metagenomic analysis.</t>
+          <t>Developing a robust biomethanation process by improving oxygen tolerance of Methanothermobacter wolfeii strain BSEL.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -23619,12 +25625,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>OR-6616F8EC469F</t>
+          <t>OR-847C7249FFAB</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spontaneous mainstream anammox in a full-scale wastewater treatment plant with hybrid sludge retention time in a temperate zone of China.</t>
+          <t>Pyocyanin-dependent electrochemical inhibition of Pseudomonas aeruginosa biofilms is synergistic with antibiotic treatment.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -23644,12 +25650,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>OR-698FFA4847F7</t>
+          <t>OR-84BE51E22B78</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>A photocatalytic Anammox@LC-COF biohybrid overcomes oxidative stress defense for resilient nitrogen removal.</t>
+          <t>Rapid and successful start-up of anammox process by immobilizing the minimal quantity of biomass in PVA-SA gel beads.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -23669,12 +25675,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>OR-69DA054B08A8</t>
+          <t>OR-84CED3EF8A62</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Facilitated extracellular electron transfer of Shewanella loihica PV-4 by antimony-doped tin oxide nanoparticles as active microelectrodes.</t>
+          <t>Microbial Ecology of Coastal Ecosystems: Investigations of the Genetic Potential for Anaerobic Hydrocarbon Transformation and the Response to Hydrocarbon Exposure</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -23694,12 +25700,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>OR-6CAE850AD459</t>
+          <t>OR-872AA1CCF621</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ArnR binds a [4Fe-4S] cluster and indirectly senses anaerobicity in Corynebacteria.</t>
+          <t>Genome-guided analysis of physiological capacities of Tepidanaerobacter acetatoxydans provides insights into environmental adaptations and syntrophic acetate oxidation.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -23719,12 +25725,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>OR-6D00DC189CB1</t>
+          <t>OR-881AE66015C9</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Development of a novel human intestinal model to elucidate the effect of anaerobic commensals on Escherichia coli infection.</t>
+          <t>Corrosion behaviour and biocorrosion of galvanized steel water distribution systems.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -23744,12 +25750,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>OR-6D1F6319B015</t>
+          <t>OR-88628A19662D</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>A novel approach for achieving high enrichment of anammox and nitrogen removal rate in municipal wastewater treatment: A pure biofilm process.</t>
+          <t>Modeling of simultaneous denitrification--anaerobic digestion--organic matter aerobic oxidation and nitrification in an anoxic-anaerobic-aerobic compact filter reactor.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -23769,12 +25775,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OR-6D34644D86D9</t>
+          <t>OR-8B7804C5D4FE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>A low-cost microbial fuel cell based sensor for in-situ monitoring of dissolved oxygen for over half a year.</t>
+          <t>Exploring the effects of microaeration on the conversion of hexadecane to methane</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -23794,12 +25800,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OR-6FAF906F2BA4</t>
+          <t>OR-8C9C4EB5EAD5</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>The Selenoproteome as a Dynamic Response Mechanism to Oxidative Stress in Hydrogenotrophic Methanogenic Communities.</t>
+          <t>Purification of high ammonia wastewater in a biofilm airlift loop bioreactor with microbial communities analysis.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -23819,12 +25825,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OR-77805E828A28</t>
+          <t>OR-8D002429B9F6</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>In Situ Spectroelectrochemical Characterization Reveals Cytochrome-Mediated Electric Syntrophy in Geobacter Coculture.</t>
+          <t>A critical review of the oxygen paradox in mainstream anaerobic ammonium oxidation: dissolved oxygen as a cross-scale driver from microbial adaptation to process stability.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -23844,12 +25850,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>OR-7E9ABB53F760</t>
+          <t>OR-9440AF0B4A4B</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Combination of upflow anaerobic sludge blanket (UASB) reactor and partial nitritation/anammox moving bed biofilm reactor (MBBR) for municipal wastewater treatment.</t>
+          <t>Characterizing algal-bacterial symbiotic biofilms: Insights into coexistence of algae and anaerobic microorganisms.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -23869,12 +25875,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>OR-7F64C2887E13</t>
+          <t>OR-9708A67CA67B</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa Exhibits Deficient Biofilm Formation in the Absence of Class II and III Ribonucleotide Reductases Due to Hindered Anaerobic Growth.</t>
+          <t>Waterlogging and hypoxia in plant abiotic stress.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -23894,12 +25900,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>OR-81B738B20350</t>
+          <t>OR-978C0281B7C6</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Developing a robust biomethanation process by improving oxygen tolerance of Methanothermobacter wolfeii strain BSEL.</t>
+          <t>Redox zones stratification and the microbial community characteristics in a periphyton bioreactor.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -23919,12 +25925,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>OR-847C7249FFAB</t>
+          <t>OR-9E8EB00A42FB</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Pyocyanin-dependent electrochemical inhibition of Pseudomonas aeruginosa biofilms is synergistic with antibiotic treatment.</t>
+          <t>Electro-mediated cathodic oxygen drives respiration chain electron transfer of electroactive bacteria to enhance refractory organic biological oxidation.</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -23944,12 +25950,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>OR-84BE51E22B78</t>
+          <t>OR-A85BF22D7826</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Rapid and successful start-up of anammox process by immobilizing the minimal quantity of biomass in PVA-SA gel beads.</t>
+          <t>Anaerobic fluorescent reporters for live imaging of Pseudomonas aeruginosa.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -23969,12 +25975,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OR-84CED3EF8A62</t>
+          <t>OR-AB7A2512C5BF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Microbial Ecology of Coastal Ecosystems: Investigations of the Genetic Potential for Anaerobic Hydrocarbon Transformation and the Response to Hydrocarbon Exposure</t>
+          <t>Chronic high-dose silver nanoparticle exposure stimulates N2O emissions by constructing anaerobic micro-environment.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -23994,12 +26000,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OR-872AA1CCF621</t>
+          <t>OR-AC538994A278</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Genome-guided analysis of physiological capacities of Tepidanaerobacter acetatoxydans provides insights into environmental adaptations and syntrophic acetate oxidation.</t>
+          <t>Aerobic radical polymerization mediated by microbial metabolism.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -24019,12 +26025,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OR-881AE66015C9</t>
+          <t>OR-AD18DFF4BF1E</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Corrosion behaviour and biocorrosion of galvanized steel water distribution systems.</t>
+          <t>Anaerobic Oxidation of Methane Coupled with Dissimilatory Nitrate Reduction to Ammonium Fuels Anaerobic Ammonium Oxidation.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -24044,12 +26050,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OR-88628A19662D</t>
+          <t>OR-B0BC2C50F510</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Modeling of simultaneous denitrification--anaerobic digestion--organic matter aerobic oxidation and nitrification in an anoxic-anaerobic-aerobic compact filter reactor.</t>
+          <t>Microbial Community Structure Along a Horizontal Oxygen Gradient in a Costa Rican Volcanic Influenced Acid Rock Drainage System.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -24069,12 +26075,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OR-8B7804C5D4FE</t>
+          <t>OR-B9BE2F0A2077</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Exploring the effects of microaeration on the conversion of hexadecane to methane</t>
+          <t>Beyond climate: the emerging physiological roles of methane and nitrous oxide</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -24094,12 +26100,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OR-8C9C4EB5EAD5</t>
+          <t>OR-BC899FA48468</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Purification of high ammonia wastewater in a biofilm airlift loop bioreactor with microbial communities analysis.</t>
+          <t>Sediment-water interface reoxygenation by NO3-LDH promotes tetracycline degradation in sediments and modulates antibiotic resistance gene dynamics.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -24119,12 +26125,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>OR-8D002429B9F6</t>
+          <t>OR-BCD134E63CCC</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>A critical review of the oxygen paradox in mainstream anaerobic ammonium oxidation: dissolved oxygen as a cross-scale driver from microbial adaptation to process stability.</t>
+          <t>A VOLTAMMETRIC FLAVIN MICROELECTRODE FOR USE IN BIOFILMS.</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -24144,12 +26150,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OR-9440AF0B4A4B</t>
+          <t>OR-BD850415CFF0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Characterizing algal-bacterial symbiotic biofilms: Insights into coexistence of algae and anaerobic microorganisms.</t>
+          <t>Achieving nitritation and anammox enrichment in a single moving-bed biofilm reactor treating reject water.</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -24169,12 +26175,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OR-9708A67CA67B</t>
+          <t>OR-BF325A4DD529</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Waterlogging and hypoxia in plant abiotic stress.</t>
+          <t>Optimization of a mainstream nitritation-denitritation process and anammox polishing.</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -24194,12 +26200,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OR-978C0281B7C6</t>
+          <t>OR-C1446C289F10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Redox zones stratification and the microbial community characteristics in a periphyton bioreactor.</t>
+          <t>Optimization and Mechanistic Understanding for Value-added Products Production through Anaerobic Digestion</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -24219,12 +26225,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>OR-9E8EB00A42FB</t>
+          <t>OR-C2819C2E9DA6</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Electro-mediated cathodic oxygen drives respiration chain electron transfer of electroactive bacteria to enhance refractory organic biological oxidation.</t>
+          <t>Oxygen exposure and diffusion are key formulation barriers in the microencapsulation of extremely oxygen-sensitive next-generation probiotics.</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24244,12 +26250,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>OR-A85BF22D7826</t>
+          <t>OR-C4E46D0EC4DF</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Anaerobic fluorescent reporters for live imaging of Pseudomonas aeruginosa.</t>
+          <t>N2O micro-profiles in biofilm from a one-stage autotrophic nitrogen removal system by microelectrode.</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24269,12 +26275,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OR-AB7A2512C5BF</t>
+          <t>OR-D4E28CE4FEBA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chronic high-dose silver nanoparticle exposure stimulates N2O emissions by constructing anaerobic micro-environment.</t>
+          <t>Gas phase in plants: integrating physiology, ecology and environmental sciences</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24294,12 +26300,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OR-AC538994A278</t>
+          <t>OR-D6DD506C208B</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Aerobic radical polymerization mediated by microbial metabolism.</t>
+          <t>Sustainable modulation of anaerobic malodorous black water: The interactive effect of oxygen-loaded porous material and submerged macrophyte.</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24319,12 +26325,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OR-AD18DFF4BF1E</t>
+          <t>OR-D97BC4BCDE81</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Anaerobic Oxidation of Methane Coupled with Dissimilatory Nitrate Reduction to Ammonium Fuels Anaerobic Ammonium Oxidation.</t>
+          <t>Effect of Psidium cattleianum leaf extract on enamel demineralisation and dental biofilm composition in situ.</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24344,12 +26350,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OR-B0B72D22FA67</t>
+          <t>OR-DF12A9229928</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Biofilm development in a pilot-scale gravity sewer: Physical characteristics, microstructure, and microbial communities.</t>
+          <t>Influence of dissolved oxygen concentration on the start-up of the anammox-based process: ELAN®.</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24369,12 +26375,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OR-B0BC2C50F510</t>
+          <t>OR-E259E70E4E24</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Microbial Community Structure Along a Horizontal Oxygen Gradient in a Costa Rican Volcanic Influenced Acid Rock Drainage System.</t>
+          <t>Mitochondrial Iron-Sulfur Cluster Activity and Cytosolic Iron Regulate Iron Traffic in Saccharomyces cerevisiae.</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -24394,12 +26400,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OR-B9BE2F0A2077</t>
+          <t>OR-E8A41F246699</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Beyond climate: the emerging physiological roles of methane and nitrous oxide</t>
+          <t>Effects of food waste addition on biofilm formation and sulfide production in a gravity sewer.</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -24419,12 +26425,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OR-BC899FA48468</t>
+          <t>OR-EAB26D73F72F</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Sediment-water interface reoxygenation by NO3-LDH promotes tetracycline degradation in sediments and modulates antibiotic resistance gene dynamics.</t>
+          <t>[Start-up of CANON Process and Short-cut Nitrification in a Pilot-scale MBBR Reactor].</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -24444,12 +26450,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OR-BCD134E63CCC</t>
+          <t>OR-ED32913CBCA0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>A VOLTAMMETRIC FLAVIN MICROELECTRODE FOR USE IN BIOFILMS.</t>
+          <t>Oxygen response and tolerance mechanisms in Clostridioides difficile.</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -24469,12 +26475,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OR-BD850415CFF0</t>
+          <t>OR-EDB9FA156758</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Achieving nitritation and anammox enrichment in a single moving-bed biofilm reactor treating reject water.</t>
+          <t>Upflow blanket filter anammox (UBFA) system treating low-nitrogen wastewater: high-efficient nitrogen removal, granules formation, N2O emission, and microbial succession.</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -24494,12 +26500,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OR-BF325A4DD529</t>
+          <t>OR-EE4AE87CEA64</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Optimization of a mainstream nitritation-denitritation process and anammox polishing.</t>
+          <t>The FeoC [4Fe-4S] Cluster Is Redox-Active and Rapidly Oxygen-Sensitive.</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -24519,12 +26525,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OR-C1446C289F10</t>
+          <t>OR-F02D94FC55AC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Optimization and Mechanistic Understanding for Value-added Products Production through Anaerobic Digestion</t>
+          <t>Arginine Exposure Decreases Acidogenesis in Long-Term Oral Biofilm Microcosms.</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -24544,12 +26550,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OR-C2819C2E9DA6</t>
+          <t>OR-F3C64571A736</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Oxygen exposure and diffusion are key formulation barriers in the microencapsulation of extremely oxygen-sensitive next-generation probiotics.</t>
+          <t>[In-situ Phosphorus Removal Activity and Impact of the Organic Matter Concentration on Denitrifying Phosphorus Removal in Sludge Aggregates].</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -24569,12 +26575,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OR-C4E46D0EC4DF</t>
+          <t>OR-F3CDA434DF28</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>N2O micro-profiles in biofilm from a one-stage autotrophic nitrogen removal system by microelectrode.</t>
+          <t>Simultaneous phosphorus uptake and denitrification by EBPR-r biofilm under aerobic conditions: effect of dissolved oxygen.</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -24594,12 +26600,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OR-D4E28CE4FEBA</t>
+          <t>OR-F55A395D44C3</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Gas phase in plants: integrating physiology, ecology and environmental sciences</t>
+          <t>Biostimulation of Indigenous Microbial Community for Bioremediation of Petroleum Refinery Sludge.</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -24619,12 +26625,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OR-D6DD506C208B</t>
+          <t>OR-FCDDB5D0A4E7</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sustainable modulation of anaerobic malodorous black water: The interactive effect of oxygen-loaded porous material and submerged macrophyte.</t>
+          <t>Effect of Oxygen Gradient on the Organic Degradation and Power Performance of Single Sediment Microbial Fuel Cells</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -24644,12 +26650,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OR-D97BC4BCDE81</t>
+          <t>OR-FFE59AE69E26</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Effect of Psidium cattleianum leaf extract on enamel demineralisation and dental biofilm composition in situ.</t>
+          <t>[Effect of Different Ratios of Anaerobic Time and Aeration Time on the Operation of a Continuous-Flow Reactor with Partial Nitrification Granules].</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -24669,12 +26675,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OR-DF12A9229928</t>
+          <t>R00074</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Influence of dissolved oxygen concentration on the start-up of the anammox-based process: ELAN®.</t>
+          <t>Bench Scale Study for Oxygen Uptake and Anaerobic Digestion of Industrial Wastewater</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -24694,12 +26700,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OR-E259E70E4E24</t>
+          <t>R00516</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Mitochondrial Iron-Sulfur Cluster Activity and Cytosolic Iron Regulate Iron Traffic in Saccharomyces cerevisiae.</t>
+          <t>Aeration and pH Combined Regulation for the Phase Separation of Anaerobic Digestion</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -24719,12 +26725,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OR-E8A41F246699</t>
+          <t>R00608</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Effects of food waste addition on biofilm formation and sulfide production in a gravity sewer.</t>
+          <t>Comparative Study of Micro-aerobic and Anaerobic Hydrolysis Acidifications of Petrochemical Wastewater</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -24744,12 +26750,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OR-EAB26D73F72F</t>
+          <t>R00915</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>[Start-up of CANON Process and Short-cut Nitrification in a Pilot-scale MBBR Reactor].</t>
+          <t>Redox potential control and applications in microaerobic and anaerobic fermentations</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -24769,12 +26775,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OR-ED32913CBCA0</t>
+          <t>R02172</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Oxygen response and tolerance mechanisms in Clostridioides difficile.</t>
+          <t>The Road to Energy Autarky in Municipal Water Resource Recovery Facilities</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24794,12 +26800,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>OR-EDB9FA156758</t>
+          <t>R02819</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Upflow blanket filter anammox (UBFA) system treating low-nitrogen wastewater: high-efficient nitrogen removal, granules formation, N2O emission, and microbial succession.</t>
+          <t>Technical, Economical, and Microbiological Aspects of the Microaerobic Process on H2S Removal for Low Sulfate Concentration Wastewaters</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24819,12 +26825,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OR-EE4AE87CEA64</t>
+          <t>R03575</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>The FeoC [4Fe-4S] Cluster Is Redox-Active and Rapidly Oxygen-Sensitive.</t>
+          <t>The effects of pre-aeration and inoculation on solid-state anaerobic digestion of rice straw</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24844,12 +26850,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>OR-F02D94FC55AC</t>
+          <t>R03900</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Arginine Exposure Decreases Acidogenesis in Long-Term Oral Biofilm Microcosms.</t>
+          <t>Efficiency, granulation, and bacterial populations related to pollutant removal in an upflow microaerobic sludge reactor treating wastewater with low COD/TN ratio</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24869,12 +26875,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>OR-F3C64571A736</t>
+          <t>R04074</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>[In-situ Phosphorus Removal Activity and Impact of the Organic Matter Concentration on Denitrifying Phosphorus Removal in Sludge Aggregates].</t>
+          <t>Lab-scale evaluation of aerated burial concept for treatment and emergency disposal of infectious animal carcasses</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24894,12 +26900,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OR-F3CDA434DF28</t>
+          <t>R04899</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Simultaneous phosphorus uptake and denitrification by EBPR-r biofilm under aerobic conditions: effect of dissolved oxygen.</t>
+          <t>Intermittent micro-aeration: New strategy to control volatile fatty acid accumulation in high organic loading anaerobic digestion</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24919,12 +26925,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OR-F55A395D44C3</t>
+          <t>R05823</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Biostimulation of Indigenous Microbial Community for Bioremediation of Petroleum Refinery Sludge.</t>
+          <t>Metagenome metabolic analysis revealing the mechanism of simultaneous methanogenesis, aerobic methane oxidation and denitrification ( SMAMOD ) in a microaerobic up‐flow sludge bed biofilm reactor</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -24944,12 +26950,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>OR-FCDDB5D0A4E7</t>
+          <t>R06078</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Effect of Oxygen Gradient on the Organic Degradation and Power Performance of Single Sediment Microbial Fuel Cells</t>
+          <t>Self-sustaining treatment as a novel alternative for the stabilization of anaerobic digestate</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -24969,12 +26975,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>OR-FFE59AE69E26</t>
+          <t>R07479</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>[Effect of Different Ratios of Anaerobic Time and Aeration Time on the Operation of a Continuous-Flow Reactor with Partial Nitrification Granules].</t>
+          <t>Assessment of shock pretreatment and alkali pretreatment on corn stover using enzymatic hydrolysis</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -24994,12 +27000,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>R00074</t>
+          <t>R07808</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bench Scale Study for Oxygen Uptake and Anaerobic Digestion of Industrial Wastewater</t>
+          <t>Evaluating the Effects of Different Pretreatments on Anaerobic Digestion of Waste Activated Sludge Containing Polystyrene Microplastics</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -25019,12 +27025,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>R00516</t>
+          <t>R09107</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Aeration and pH Combined Regulation for the Phase Separation of Anaerobic Digestion</t>
+          <t>Innovative passive aeration process for synthetic deoxygenated water</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -25044,12 +27050,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>R00608</t>
+          <t>R10037</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Comparative Study of Micro-aerobic and Anaerobic Hydrolysis Acidifications of Petrochemical Wastewater</t>
+          <t>Dissolved oxygen drives heterotrophic microorganism succession to regulate low carbon source wastewater treatment enhanced by slurry</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -25069,12 +27075,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>R00915</t>
+          <t>R10377</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Redox potential control and applications in microaerobic and anaerobic fermentations</t>
+          <t>Influence of micro-aeration in the production of volatile fatty acids (VFA) from wastewaters with high salinity</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -25094,12 +27100,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>R02172</t>
+          <t>R11658</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>The Road to Energy Autarky in Municipal Water Resource Recovery Facilities</t>
+          <t>IMPACT OF MICRO-AERATION ON FUNGAL COMMUNITY FROM ANAEROBIC DIGESTION</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -25119,12 +27125,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>R02819</t>
+          <t>R11693</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Technical, Economical, and Microbiological Aspects of the Microaerobic Process on H2S Removal for Low Sulfate Concentration Wastewaters</t>
+          <t>In-situ intermittent micro-aeration in food waste and sewage sludge anaerobic co-digestion: Performance, stability, and microbial dynamics</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -25144,12 +27150,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>R03575</t>
+          <t>R12556</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>The effects of pre-aeration and inoculation on solid-state anaerobic digestion of rice straw</t>
+          <t>Advancing microbial electrochemical technologies for the circular economy, energy resilience, and environmental sustainability</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -25169,12 +27175,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>R03900</t>
+          <t>R13274</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Efficiency, granulation, and bacterial populations related to pollutant removal in an upflow microaerobic sludge reactor treating wastewater with low COD/TN ratio</t>
+          <t>Micro-aeration enhances lactic acid production in food waste fermentation</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -25194,12 +27200,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>R04074</t>
+          <t>R13623</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Lab-scale evaluation of aerated burial concept for treatment and emergency disposal of infectious animal carcasses</t>
+          <t>Single-stage C-N-P removal and ultra-low net sludge production driven by cyclic oxygen exposure and side-stream acidogenesis in an intermittent-aeration IFAS-OSA system</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -25219,12 +27225,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>R04899</t>
+          <t>R13817</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Intermittent micro-aeration: New strategy to control volatile fatty acid accumulation in high organic loading anaerobic digestion</t>
+          <t>Micro-aeration unlocks endogenous nitrogen removal in anaerobic digesters via metabolically versatile fermentative bacteria</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -25244,12 +27250,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>R05611</t>
+          <t>R13836</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Enhanced hydrolysis and acidification of cellulose at high loading for methane production via anaerobic digestion supplemented with high mobility nanobubble water</t>
+          <t>Enhancement of surfactant biodegradation with an anaerobic membrane bioreactor by introducing microaeration.</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25269,12 +27275,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>R05823</t>
+          <t>R13840</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Metagenome metabolic analysis revealing the mechanism of simultaneous methanogenesis, aerobic methane oxidation and denitrification ( SMAMOD ) in a microaerobic up‐flow sludge bed biofilm reactor</t>
+          <t>Coupling of membrane-based bubbleless micro-aeration for 2,4-dinitrophenol degradation in a hydrolysis acidification reactor.</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25294,12 +27300,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>R06078</t>
+          <t>R13856</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Self-sustaining treatment as a novel alternative for the stabilization of anaerobic digestate</t>
+          <t>Strategy to enhance semi-continuous anaerobic digestion of food waste by combined use of calcium peroxide and magnetite</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -25319,12 +27325,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>R06227</t>
+          <t>R13882</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Using air instead of biogas for mixing and its effect on anaerobic digestion of animal wastewater with high suspended solids</t>
+          <t>Practical approaches for retrofitting plug flow digester and process control to maximize hydrolysis and methane yield from piggery waste</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -25344,12 +27350,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>R07479</t>
+          <t>R13920</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Assessment of shock pretreatment and alkali pretreatment on corn stover using enzymatic hydrolysis</t>
+          <t>Nanobubbles drive advanced anaerobic treatment of swine wastewater for efficient methane recovery: Performance gains and multi-pathway enhancement</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25369,12 +27375,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>R07808</t>
+          <t>R13959</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Evaluating the Effects of Different Pretreatments on Anaerobic Digestion of Waste Activated Sludge Containing Polystyrene Microplastics</t>
+          <t>Influence of Temperature and Oxidation-Reduction Potential on Hydrolysis of Swine Manure Wastewater</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25394,12 +27400,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>R09107</t>
+          <t>R13964</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Innovative passive aeration process for synthetic deoxygenated water</t>
+          <t>Hydrogen sulphide management in anaerobic digestion: A critical review on input control, process regulation, and post-treatment</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25419,12 +27425,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>R09240</t>
+          <t>R13970</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Microbubble Intensification of Bioprocessing</t>
+          <t>Anaerobic and microaerobic treatment of synthetic BTEX contaminated waters</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25438,508 +27444,8 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>R10037</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Dissolved oxygen drives heterotrophic microorganism succession to regulate low carbon source wastewater treatment enhanced by slurry</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>R10377</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Influence of micro-aeration in the production of volatile fatty acids (VFA) from wastewaters with high salinity</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>R11658</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>IMPACT OF MICRO-AERATION ON FUNGAL COMMUNITY FROM ANAEROBIC DIGESTION</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>R11693</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>In-situ intermittent micro-aeration in food waste and sewage sludge anaerobic co-digestion: Performance, stability, and microbial dynamics</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>R12556</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Advancing microbial electrochemical technologies for the circular economy, energy resilience, and environmental sustainability</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>R13274</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Micro-aeration enhances lactic acid production in food waste fermentation</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>R13280</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Microaeration Process Design, Control, and Monitoring for Biogas Desulfurization in Anaerobic Digestion</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>R13623</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Single-stage C-N-P removal and ultra-low net sludge production driven by cyclic oxygen exposure and side-stream acidogenesis in an intermittent-aeration IFAS-OSA system</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>R13817</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Micro-aeration unlocks endogenous nitrogen removal in anaerobic digesters via metabolically versatile fermentative bacteria</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>R13833</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Insight into the Role of Facultative Bacteria Stimulated by Microaeration in Continuous Bioreactors Converting LCFA to Methane</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>204</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>R13836</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Enhancement of surfactant biodegradation with an anaerobic membrane bioreactor by introducing microaeration.</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>205</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>R13840</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Coupling of membrane-based bubbleless micro-aeration for 2,4-dinitrophenol degradation in a hydrolysis acidification reactor.</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>206</v>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>R13856</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Strategy to enhance semi-continuous anaerobic digestion of food waste by combined use of calcium peroxide and magnetite</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>R13882</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Practical approaches for retrofitting plug flow digester and process control to maximize hydrolysis and methane yield from piggery waste</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>R13920</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Nanobubbles drive advanced anaerobic treatment of swine wastewater for efficient methane recovery: Performance gains and multi-pathway enhancement</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>R13923</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Nanobubble technology to enhance energy recovery from anaerobic digestion of organic solid wastes: Potential mechanisms and recent advancements</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>R13944</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Oxidation-Reduction Potential-Based Micro-Aeration Control System for Anaerobic Digestion.</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>R13959</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Influence of Temperature and Oxidation-Reduction Potential on Hydrolysis of Swine Manure Wastewater</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>R13964</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Hydrogen sulphide management in anaerobic digestion: A critical review on input control, process regulation, and post-treatment</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>R13970</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Anaerobic and microaerobic treatment of synthetic BTEX contaminated waters</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>先题名/摘要专题判断；优先产甲烷结构/传质，非AD方法参照单列</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E214"/>
+  <autoFilter ref="A1:E194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25950,7 +27456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26009,6 +27515,21 @@
           <t>targets</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>three_D_method_reported_in_abstract</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fulltext_3D_verified</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>whole_aggregate_3D_verified</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26114,17 +27635,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ODS-PMID32994285</t>
+          <t>ODS-PMID18405985</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Size Shapes the Active Microbiome of Methanogenic Granules, Corroborating a Biofilm Life Cycle.</t>
+          <t>Correlative light/electron microscopy for the investigation of microbial mats from Black Sea Cold Seeps.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.1128/msystems.00323-20</t>
+          <t>10.1016/j.mimet.2008.02.020</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -26134,90 +27655,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>不同粒径级中，H2底物产甲烷活性高于VFA底物；中等粒径群落最活跃，粒径对活跃群落组成影响大于底物</t>
+          <t>黑海冷泉微生物席用树脂切片和荧光/胶体金凝集素定位EPS，比较光学与电镜图</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>粒径相关不自动证明扩散限制；同时可能反映生物膜年龄、群落和底物利用差异；16S转录不是全部通量</t>
+          <t>是切片相关显微，并非已核实整颗粒三维重建；EPS黏附/矿化作用不等于氧屏障或孔隙流量</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID32994285", "identity_field": "paper_id"}]</t>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID18405985", "identity_field": "paper_id"}]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>粒径分级＋活性与扩增子；非三维结构测量</t>
+          <t>树脂切片，光/电镜相关成像＋凝集素标记EPS</t>
         </is>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>["EPS", "细菌/古菌聚集"]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OR-06716459121E</t>
+          <t>ODS-PMID29150508</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Co-cultivation of the strictly anaerobic methanogen Methanosarcina barkeri with aerobic methanotrophs in an oxygen-limited membrane bioreactor.</t>
+          <t>Community Composition and Ultrastructure of a Nitrate-Dependent Anaerobic Methane-Oxidizing Enrichment Culture.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10.1007/s00253-018-9038-x</t>
+          <t>10.1128/aem.02186-17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>全文相关方法/结果段落；复用仓库原件，非全文通读</t>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5 L工作体积、150 rpm；气流先5后10 mL/min，空气2.38后2.86 mL/min；DO持续低于约3 μM检出限，同时供入氧并维持共培养</t>
+          <t>FISH/免疫金/电子断层揭示Ca.Methanoperedens细胞约1.5 μm、管状突出和候选细胞接触结构</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>原文是调节气体组成、连续监测DO，并非DO设定点闭环曝气；FISH聚集不等于局部氧保护已直接测得；气流分项之和与总量的原文表述保留，不自行补齐</t>
+          <t>电子断层方法由摘要明确；本轮未读正文确认重建体积/分辨率；细胞接触功能未证，不能认定导电或气体通道</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-06716459121E", "identity_field": "id"}]</t>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID29150508", "identity_field": "paper_id"}]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FISH；未核实三维堆栈</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
+          <t>含electron tomography的光/电镜、FISH、免疫金</t>
+        </is>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>["古菌细胞/候选接触结构"]</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OR-8E58C5BBDB53</t>
+          <t>ODS-PMID32994285</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stratified microbial structure and activity in sulfide- and methane-producing anaerobic sewer biofilms.</t>
+          <t>Size Shapes the Active Microbiome of Methanogenic Granules, Corroborating a Biofilm Life Cycle.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.1128/aem.02146-14</t>
+          <t>10.1128/msystems.00323-20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -26227,50 +27767,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>约800 μm生物膜；硫化物主要在0–300 μm产生；产甲烷古菌偏内层，成像与模型相符</t>
+          <t>不同粒径级中，H2底物产甲烷活性高于VFA底物；中等粒径群落最活跃，粒径对活跃群落组成影响大于底物</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>微电极测量不等于测了氧；摘要尚不能确认二维切片与三维重建方式；没有氧冲击保护的独立干预</t>
+          <t>粒径相关不自动证明扩散限制；同时可能反映生物膜年龄、群落和底物利用差异；16S转录不是全部通量</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-8E58C5BBDB53", "identity_field": "id"}]</t>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID32994285", "identity_field": "paper_id"}]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>冷冻切片FISH＋微电极＋模型（摘要）</t>
+          <t>粒径分级＋活性与扩增子；非三维结构测量</t>
         </is>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>["SRB", "产甲烷古菌", "硫化物"]</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OR-F8559A118DBF</t>
+          <t>ODS-PMID35699440</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Use of an oxygen planar optode to assess the effect of high velocity microsprays on oxygen penetration in a human dental biofilms in-vitro.</t>
+          <t>Stimulating Effect of Trichococcus flocculiformis on a Coculture of Syntrophomonas wolfei and Methanospirillum hungatei .</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.1186/s12903-020-01217-0</t>
+          <t>10.1128/aem.00391-22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -26280,22 +27812,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>高速微喷去除部分牙科生物膜后，基底由无氧快速变有氧</t>
+          <t>Trichococcus加入Syntrophomonas—产甲烷菌共培养后丁酸消费和甲烷率升高；SEM见共聚集倾向</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>平面DO图不是三维体成像，宿主牙膜与AD不同；去除生物量与传质路径共变</t>
+          <t>功能提高可能涉及信号调节或酶表达，不证明距离缩短导致H2/甲酸通量提高；非真三维成像</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-F8559A118DBF", "identity_field": "id"}]</t>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID35699440", "identity_field": "paper_id"}]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>平面光极，二维DO图</t>
+          <t>SEM表面形态，未核实三维重建</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -26305,17 +27837,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R13832</t>
+          <t>ODS-PMID40222284</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A membrane aerated biofilm reactor for sulfide control from anaerobically treated wastewater.</t>
+          <t>Facilitating anaerobic digestion of kitchen waste through diatomite-mediated spatial ecological niches construction.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10.1080/09593330.2018.1441329</t>
+          <t>10.1016/j.wasman.2025.114792</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -26325,30 +27857,356 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>硅胶管供氧，硫化物去除约90%，pH7.5时H2S去除98%；群落在膜上有分层</t>
+          <t>10 g/L硅藻土使甲烷提高11.76%；发酵菌偏紧密附着，产乙酸型与氢营养古菌富集于悬浮组</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>测序分层不是已核实三维成像；硫化物物种受pH影响，不能将去除率等同跨膜O2通量</t>
+          <t>群落分级不是三维细胞坐标，电子传递/互营解释未测H2/甲酸通量；载体吸附与缓冲亦可能参与</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "R13832", "identity_field": "id"}]</t>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID40222284", "identity_field": "paper_id"}]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>摘要测序/膜壁定位描述；三维成像未核实</t>
+          <t>群落分级/生物膜和EPS；三维位置未核实</t>
         </is>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OR-06716459121E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Co-cultivation of the strictly anaerobic methanogen Methanosarcina barkeri with aerobic methanotrophs in an oxygen-limited membrane bioreactor.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10.1007/s00253-018-9038-x</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>全文相关方法/结果段落；复用仓库原件，非全文通读</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.5 L工作体积、150 rpm；气流先5后10 mL/min，空气2.38后2.86 mL/min；DO持续低于约3 μM检出限，同时供入氧并维持共培养</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>原文是调节气体组成、连续监测DO，并非DO设定点闭环曝气；FISH聚集不等于局部氧保护已直接测得；气流分项之和与总量的原文表述保留，不自行补齐</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-06716459121E", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FISH；未核实三维堆栈</t>
+        </is>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OR-1925EF467A30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Microbial stratification protects denitrifying anaerobic methane oxidation archaea and bacteria from external oxygen shock in membrane biofilm reactor.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10.1016/j.biortech.2023.129966</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DO0.2 mg/L时目标类群显著下降，0.5 mg/L出现硝酸盐积累；作者提出外层替代保护内层</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>仅摘要未确认氧微剖面或因果保护；不是产甲烷AD；功能基因下降非速率</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-1925EF467A30", "identity_field": "id"}, {"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "OR-1925EF467A30", "identity_field": "paper_id"}]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>分层保护来自作者解释；三维/局部DO测量待正文</t>
+        </is>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OR-52E6BA12BEDD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Spatial distribution and viability of nitrifying, denitrifying and ANAMMOX bacteria in biofilms of sponge media retrieved from a full-scale biological nutrient removal plant.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10.1007/s00449-012-0701-9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FISH与离子微电极显示侧面/中心菌群不同，生物量随深度减而存活率不表现同样空间变化，Anammox贯穿深度</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>空间位置不等于相同DO，非产甲烷菌；摘要FISH不自动算3D体重建</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-52E6BA12BEDD", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FISH与NH4/NO3微电极；三维未核实</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OR-8E58C5BBDB53</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Stratified microbial structure and activity in sulfide- and methane-producing anaerobic sewer biofilms.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.1128/aem.02146-14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>约800 μm生物膜；硫化物主要在0–300 μm产生；产甲烷古菌偏内层，成像与模型相符</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>微电极测量不等于测了氧；摘要尚不能确认二维切片与三维重建方式；没有氧冲击保护的独立干预</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-8E58C5BBDB53", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>冷冻切片FISH＋微电极＋模型（摘要）</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>["SRB", "产甲烷古菌", "硫化物"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OR-B0B72D22FA67</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Biofilm development in a pilot-scale gravity sewer: Physical characteristics, microstructure, and microbial communities.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10.1016/j.envres.2021.110838</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>45 d厚约1.2 mm，局部ORP−105 mV及约0.1 μmol/L硫化物；结构和类群变化相关</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>负ORP不是直接DO证明；微电极种类要分清，不把ORP剖面写为氧剖面</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-B0B72D22FA67", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>微结构分析＋微电极；三维方法未核实</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OR-F8559A118DBF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Use of an oxygen planar optode to assess the effect of high velocity microsprays on oxygen penetration in a human dental biofilms in-vitro.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10.1186/s12903-020-01217-0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>高速微喷去除部分牙科生物膜后，基底由无氧快速变有氧</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>平面DO图不是三维体成像，宿主牙膜与AD不同；去除生物量与传质路径共变</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "OR-F8559A118DBF", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>平面光极，二维DO图</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R13832</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A membrane aerated biofilm reactor for sulfide control from anaerobically treated wastewater.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10.1080/09593330.2018.1441329</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>硅胶管供氧，硫化物去除约90%，pH7.5时H2S去除98%；群落在膜上有分层</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>测序分层不是已核实三维成像；硫化物物种受pH影响，不能将去除率等同跨膜O2通量</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "R13832", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>摘要测序/膜壁定位描述；三维成像未核实</t>
+        </is>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:N15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26359,7 +28217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26660,8 +28518,80 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R06227</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Using air instead of biogas for mixing and its effect on anaerobic digestion of animal wastewater with high suspended solids</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.1016/j.biortech.2020.124047</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>相同功率下摘要报告均匀混合时间由10 min缩短到1.5 min，甲烷及水解改善</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>氧输入和对流同时改变；62.9%/37.1%的贡献分摊方法需正文核；混合时间不是Deff、kf或kLa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "R06227", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>bulk homogeneous mixing time</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10 versus 1.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>摘要报告同功率混合试验；示踪/拟合细节待全文</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>机械混合vs空气混合；动物废水AD</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>完整缓存摘要</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>不是聚集体内部Deff或细胞间距离</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P4"/>
+  <autoFilter ref="A1:P5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26672,7 +28602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26788,17 +28718,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ODS-PMID36374033</t>
+          <t>ODS-PMID35699440</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Interspecies Formate Exchange Drives Syntrophic Growth of Syntrophotalea carbinolica and Methanococcus maripaludis.</t>
+          <t>Stimulating Effect of Trichococcus flocculiformis on a Coculture of Syntrophomonas wolfei and Methanospirillum hungatei .</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.1128/aem.01159-22</t>
+          <t>10.1128/aem.00391-22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -26808,27 +28738,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>H2/甲酸代谢突变株竞争说明甲酸交换占优势；搅拌促进H2向顶空损失时，能利用甲酸的菌株优势更大</t>
+          <t>Trichococcus加入Syntrophomonas—产甲烷菌共培养后丁酸消费和甲烷率升高；SEM见共聚集倾向</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>证明载体选择与搅拌相关，不是给出了菌间距离、絮体内外通量；不将甲酸等同H2气泡</t>
+          <t>功能提高可能涉及信号调节或酶表达，不证明距离缩短导致H2/甲酸通量提高；非真三维成像</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID36374033", "identity_field": "paper_id"}]</t>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID35699440", "identity_field": "paper_id"}]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>["formate", "H2"]</t>
+          <t>["H2/formate（互营背景，具体分摊未实测）"]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>突变株竞争＋搅拌干预（摘要）</t>
+          <t>加入伙伴干预＋速率和SEM，交换路径仍待证</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -26838,8 +28768,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ODS-PMID35918706</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Integrating metagenomic binning with flux balance analysis to unravel syntrophies in anaerobic CO 2 methanation.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10.1186/s40168-022-01311-1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4个外置沼气升级反应器扩散装置上的生物膜，基因组/通量平衡预测甲酸和氨基酸交换网络</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>共同出现和FBA不是物质通量/细胞间距离实测；不把名称flux balance当已经测到通量</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID35918706", "identity_field": "paper_id"}]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>["H2", "CO2", "formate", "amino acids"]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>基因组重建＋通量平衡模型</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ODS-PMID36374033</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Interspecies Formate Exchange Drives Syntrophic Growth of Syntrophotalea carbinolica and Methanococcus maripaludis.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.1128/aem.01159-22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>H2/甲酸代谢突变株竞争说明甲酸交换占优势；搅拌促进H2向顶空损失时，能利用甲酸的菌株优势更大</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>证明载体选择与搅拌相关，不是给出了菌间距离、絮体内外通量；不将甲酸等同H2气泡</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/omics_dataset_discovery/paper_discovery_candidates_enriched.json", "id": "ODS-PMID36374033", "identity_field": "paper_id"}]</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>["formate", "H2"]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>突变株竞争＋搅拌干预（摘要）</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26850,7 +28886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27355,8 +29391,86 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R13944</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Oxidation-Reduction Potential-Based Micro-Aeration Control System for Anaerobic Digestion.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；正文方法/参数仍待核实</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>摘要称每24 h引入ORP基线+25 mV控制后VFA下降56%、甲烷提高252%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>年/期刊/DOI尚缺；与R07202研究链的暴露频率表述不同，需核身份和前文，不当独立支持</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[{"path": "results/ad-oxygen-literature-20261006/oxygen_response_review/catalog.json", "id": "R13944", "identity_field": "id"}]</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>摘要报告ORP间歇反馈，元数据待核</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>+25 mV above baseline</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>摘要称every24h，与R07202每隔一天不可混写</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>未核</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>原库完整摘要</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q6"/>
+  <autoFilter ref="A1:Q7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/ad-oxygen-literature-20261006/oxygen_response_review/spatial_gas_transfer/spatial_gas_transfer_cumulative.xlsx
+++ b/results/ad-oxygen-literature-20261006/oxygen_response_review/spatial_gas_transfer/spatial_gas_transfer_cumulative.xlsx
@@ -979,6 +979,16 @@
           <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/cfc7af329ca2b6a6948e25003e2b6ddc6f91b2e2dc3e867e63108f407191f658.body</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>A 产甲烷直接（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL5" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -1327,6 +1337,16 @@
           <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/cfc7af329ca2b6a6948e25003e2b6ddc6f91b2e2dc3e867e63108f407191f658.body</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>C 天然成像方法（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL8" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -1445,6 +1465,16 @@
       <c r="AC9" t="b">
         <v>0</v>
       </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>导航综述（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL9" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -2882,6 +2912,16 @@
           <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/1986329a541e64ec6ec832c62ee17bee05ca3f6c784fb52bd53d2341f1a1f8d9.body</t>
         </is>
       </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>A 产甲烷直接（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL27" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -3000,6 +3040,16 @@
       <c r="AC28" t="b">
         <v>0</v>
       </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>C DAMO/Anammox模型（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL28" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -4032,6 +4082,16 @@
       <c r="AC40" t="b">
         <v>0</v>
       </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>C DAMO/Anammox传质参照（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL40" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -4776,6 +4836,16 @@
           <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/36328184af1a8747e4473dc767f2753f5f61f250c369017f68b452c5d63ba90a.body</t>
         </is>
       </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>A 产甲烷直接（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL49" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -5371,6 +5441,16 @@
           <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/4c7b9de88dc3c2b30f7806e60e8ba11074b3948ba15c7089ac42c3b2eb226dd9.body</t>
         </is>
       </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>A 互营共培养（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL56" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -5571,6 +5651,16 @@
       <c r="AC58" t="b">
         <v>0</v>
       </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>A CO2甲烷化生物膜（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL58" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -5776,6 +5866,16 @@
           <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/4c7b9de88dc3c2b30f7806e60e8ba11074b3948ba15c7089ac42c3b2eb226dd9.body</t>
         </is>
       </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>A 产甲烷直接（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL60" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -6202,6 +6302,16 @@
       <c r="AC65" t="b">
         <v>0</v>
       </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>C 甲烷氧化脱氮膜（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL65" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -6551,6 +6661,16 @@
       <c r="AC69" t="b">
         <v>0</v>
       </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>C 甲烷氧化方法（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL69" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -7218,6 +7338,16 @@
           <t>results/ad-oxygen-literature-20261006/omics_dataset_discovery/raw/NCBI/863e1adc64fc7079316bfb5f12b86c02fb0085e72978511e95d4520981794eb8.body</t>
         </is>
       </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>A 产甲烷AD载体（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL77" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -8337,6 +8467,16 @@
       <c r="AC91" t="b">
         <v>0</v>
       </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>B 界面电子传递背景（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL91" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -9505,6 +9645,16 @@
       <c r="AC104" t="b">
         <v>0</v>
       </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>C DAMO/Anammox（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL104" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -9705,6 +9855,16 @@
       </c>
       <c r="AC106" t="b">
         <v>0</v>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>C Anammox方法参照（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
@@ -11229,6 +11389,16 @@
       <c r="AC124" t="b">
         <v>0</v>
       </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>C 脱氮生物膜方法（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL124" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -14141,6 +14311,16 @@
       <c r="AC157" t="b">
         <v>0</v>
       </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>C 天然/方法参照（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL157" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -14678,6 +14858,16 @@
       </c>
       <c r="AC163" t="b">
         <v>0</v>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>C 下水道生物膜（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
@@ -16695,6 +16885,16 @@
       <c r="AC187" t="b">
         <v>0</v>
       </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>C 其他生物膜方法（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL187" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -17274,6 +17474,16 @@
       <c r="AC194" t="b">
         <v>0</v>
       </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>A 膜气体模型（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL194" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -18201,6 +18411,16 @@
       <c r="AC203" t="b">
         <v>0</v>
       </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>A AD气泡处理（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL203" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -18489,6 +18709,16 @@
       <c r="AC206" t="b">
         <v>0</v>
       </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>C 好氧颗粒控制参照（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL206" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -18611,6 +18841,16 @@
       </c>
       <c r="AC207" t="b">
         <v>0</v>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>A AD混合干预（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
@@ -19040,6 +19280,16 @@
       <c r="AC211" t="b">
         <v>0</v>
       </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>A 脱硫模型导航（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL211" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -19237,6 +19487,16 @@
       <c r="AC213" t="b">
         <v>0</v>
       </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>导航综述（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL213" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -19836,6 +20096,16 @@
       <c r="AC220" t="b">
         <v>0</v>
       </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>导航综述（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL220" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -20133,6 +20403,16 @@
       <c r="AC223" t="b">
         <v>0</v>
       </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>A AD相关膜生物膜（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL223" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -20256,6 +20536,16 @@
       <c r="AC224" t="b">
         <v>0</v>
       </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>A 产甲烷直接（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
+      </c>
       <c r="AL224" t="inlineStr">
         <is>
           <t>空值表示本轮尚未核实，不能推断原文未报告</t>
@@ -20784,6 +21074,16 @@
       </c>
       <c r="AC230" t="b">
         <v>0</v>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>导航综述（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
@@ -20896,6 +21196,16 @@
       </c>
       <c r="AC231" t="b">
         <v>0</v>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>待核实研究线索（详见actual_finding和decision_reason；具体条件未核字段留空）</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>完整缓存摘要；具体正文位置尚待核实</t>
+        </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
